--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8A477A-58A9-4E0D-ACAF-A6594630757D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A304D3-DE7A-4BA3-B070-AB890AE762C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="153">
   <si>
     <t>UA名字</t>
   </si>
@@ -497,6 +497,9 @@
   <si>
     <t>6359</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3723</t>
   </si>
 </sst>
 </file>
@@ -862,7 +865,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C134"/>
+  <dimension ref="A1:C135"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -2060,6 +2063,14 @@
         <v>151</v>
       </c>
     </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A304D3-DE7A-4BA3-B070-AB890AE762C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD60D30-FF84-46A0-88FA-93FE1820B65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -237,9 +237,6 @@
     <t>4167</t>
   </si>
   <si>
-    <t>xqq</t>
-  </si>
-  <si>
     <t>5818</t>
   </si>
   <si>
@@ -500,6 +497,9 @@
   </si>
   <si>
     <t>3723</t>
+  </si>
+  <si>
+    <t>lxq</t>
   </si>
 </sst>
 </file>
@@ -876,7 +876,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C1" s="4"/>
     </row>
@@ -1002,7 +1002,7 @@
         <v>2</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C15" s="4"/>
     </row>
@@ -1011,7 +1011,7 @@
         <v>2</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C16" s="4"/>
     </row>
@@ -1020,7 +1020,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C17" s="4"/>
     </row>
@@ -1029,7 +1029,7 @@
         <v>2</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C18" s="4"/>
     </row>
@@ -1038,7 +1038,7 @@
         <v>2</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C19" s="4"/>
     </row>
@@ -1047,7 +1047,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C20" s="4"/>
     </row>
@@ -1056,7 +1056,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C21" s="4"/>
     </row>
@@ -1065,7 +1065,7 @@
         <v>2</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C22" s="4"/>
     </row>
@@ -1074,7 +1074,7 @@
         <v>2</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C23" s="4"/>
     </row>
@@ -1083,7 +1083,7 @@
         <v>2</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C24" s="4"/>
     </row>
@@ -1092,7 +1092,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C25" s="4"/>
     </row>
@@ -1101,7 +1101,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C26" s="4"/>
     </row>
@@ -1155,7 +1155,7 @@
         <v>1</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C32" s="4"/>
     </row>
@@ -1164,7 +1164,7 @@
         <v>1</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C33" s="4"/>
     </row>
@@ -1173,7 +1173,7 @@
         <v>1</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C34" s="4"/>
     </row>
@@ -1182,7 +1182,7 @@
         <v>1</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C35" s="4"/>
     </row>
@@ -1191,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C36" s="4"/>
     </row>
@@ -1263,7 +1263,7 @@
         <v>21</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C44" s="4"/>
     </row>
@@ -1272,7 +1272,7 @@
         <v>21</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C45" s="4"/>
     </row>
@@ -1416,7 +1416,7 @@
         <v>36</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C61" s="4"/>
     </row>
@@ -1425,7 +1425,7 @@
         <v>36</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C62" s="4"/>
     </row>
@@ -1497,7 +1497,7 @@
         <v>46</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C70" s="4"/>
     </row>
@@ -1506,13 +1506,13 @@
         <v>46</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C71" s="4"/>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>54</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>55</v>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>56</v>
@@ -1539,7 +1539,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>57</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>58</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>59</v>
@@ -1566,7 +1566,7 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>60</v>
@@ -1575,7 +1575,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>61</v>
@@ -1584,7 +1584,7 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>62</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>63</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>64</v>
@@ -1611,7 +1611,7 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>65</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>66</v>
@@ -1629,181 +1629,181 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C85" s="4"/>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C86" s="4"/>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C87" s="4"/>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C88" s="4"/>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C89" s="4"/>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="C90" s="4"/>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>67</v>
+        <v>152</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C91" s="4"/>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>67</v>
+        <v>152</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C92" s="4"/>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>67</v>
+        <v>152</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C93" s="4"/>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>67</v>
+        <v>152</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C94" s="4"/>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C95" s="4"/>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C96" s="4"/>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="C97" s="4"/>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>100</v>
       </c>
       <c r="C98" s="4"/>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C99" s="4"/>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C100" s="4"/>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C101" s="4"/>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C102" s="4"/>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C103" s="4"/>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B104" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="C104" s="4"/>
     </row>
@@ -1812,7 +1812,7 @@
         <v>21</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C105" s="4"/>
     </row>
@@ -1821,70 +1821,70 @@
         <v>1</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C106" s="4"/>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B107" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="C107" s="4"/>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B108" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="B108" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="C108" s="4"/>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C109" s="4"/>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C110" s="4"/>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>120</v>
       </c>
       <c r="C111" s="4"/>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>67</v>
+        <v>152</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C112" s="4"/>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>127</v>
       </c>
       <c r="C113" s="4"/>
     </row>
@@ -1893,43 +1893,43 @@
         <v>21</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C114" s="4"/>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C115" s="4"/>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C116" s="4"/>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C117" s="4"/>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C118" s="4"/>
     </row>
@@ -1938,7 +1938,7 @@
         <v>29</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C119" s="4"/>
     </row>
@@ -1947,7 +1947,7 @@
         <v>36</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C120" s="4"/>
     </row>
@@ -1956,23 +1956,23 @@
         <v>29</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -1980,7 +1980,7 @@
         <v>2</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -1988,23 +1988,23 @@
         <v>1</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -2012,7 +2012,7 @@
         <v>1</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
@@ -2020,23 +2020,23 @@
         <v>29</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B130" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
@@ -2044,31 +2044,31 @@
         <v>29</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B133" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD60D30-FF84-46A0-88FA-93FE1820B65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A4E8D7-8A3F-4102-8258-CB2C3DDD32AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="156">
   <si>
     <t>UA名字</t>
   </si>
@@ -500,6 +500,15 @@
   </si>
   <si>
     <t>lxq</t>
+  </si>
+  <si>
+    <t>5353</t>
+  </si>
+  <si>
+    <t>2823</t>
+  </si>
+  <si>
+    <t>3800</t>
   </si>
 </sst>
 </file>
@@ -865,7 +874,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C135"/>
+  <dimension ref="A1:C138"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -2071,6 +2080,30 @@
         <v>151</v>
       </c>
     </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A4E8D7-8A3F-4102-8258-CB2C3DDD32AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5C63B6-FD66-4A5C-AA77-39E6398E85A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="157">
   <si>
     <t>UA名字</t>
   </si>
@@ -509,6 +509,9 @@
   </si>
   <si>
     <t>3800</t>
+  </si>
+  <si>
+    <t>2337</t>
   </si>
 </sst>
 </file>
@@ -874,7 +877,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C138"/>
+  <dimension ref="A1:C139"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -2104,6 +2107,14 @@
         <v>155</v>
       </c>
     </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Huawei\Desktop\数据看板\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5C63B6-FD66-4A5C-AA77-39E6398E85A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4208AA7-F401-49A6-8AF7-F1743DFB3071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="158">
   <si>
     <t>UA名字</t>
   </si>
@@ -512,6 +512,9 @@
   </si>
   <si>
     <t>2337</t>
+  </si>
+  <si>
+    <t>5667</t>
   </si>
 </sst>
 </file>
@@ -877,7 +880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C139"/>
+  <dimension ref="A1:C140"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.88671875" style="2"/>
@@ -2115,6 +2118,14 @@
         <v>156</v>
       </c>
     </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="158">
   <si>
     <t>UA名字</t>
   </si>
@@ -497,6 +497,15 @@
   </si>
   <si>
     <t>5667</t>
+  </si>
+  <si>
+    <t>8350</t>
+  </si>
+  <si>
+    <t>4176</t>
+  </si>
+  <si>
+    <t>9418</t>
   </si>
 </sst>
 </file>
@@ -509,7 +518,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -527,13 +536,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1001,158 +1003,161 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1477,7 +1482,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C140"/>
+  <dimension ref="A1:C145"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -1493,1234 +1498,1274 @@
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="3"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="3"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="3"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="3"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="3"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C19" s="3"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C20" s="3"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C21" s="3"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="3"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="3"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C24" s="3"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C25" s="3"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C26" s="3"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="3"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C30" s="3"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C31" s="3"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C32" s="3"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C33" s="3"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C34" s="3"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C35" s="3"/>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C36" s="3"/>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C37" s="3"/>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C38" s="3"/>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C39" s="3"/>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C40" s="3"/>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="4" t="s">
         <v>44</v>
       </c>
       <c r="C41" s="3"/>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C42" s="3"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C43" s="3"/>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="4" t="s">
         <v>48</v>
       </c>
       <c r="C44" s="3"/>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="4" t="s">
         <v>49</v>
       </c>
       <c r="C45" s="3"/>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C46" s="3"/>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C47" s="3"/>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C48" s="3"/>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="4" t="s">
         <v>53</v>
       </c>
       <c r="C49" s="3"/>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="4" t="s">
         <v>54</v>
       </c>
       <c r="C50" s="3"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="4" t="s">
         <v>55</v>
       </c>
       <c r="C51" s="3"/>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="4" t="s">
         <v>57</v>
       </c>
       <c r="C52" s="3"/>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="4" t="s">
         <v>58</v>
       </c>
       <c r="C53" s="3"/>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="4" t="s">
         <v>59</v>
       </c>
       <c r="C54" s="3"/>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="4" t="s">
         <v>60</v>
       </c>
       <c r="C55" s="3"/>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="4" t="s">
         <v>61</v>
       </c>
       <c r="C56" s="3"/>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="4" t="s">
         <v>62</v>
       </c>
       <c r="C57" s="3"/>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="4" t="s">
         <v>63</v>
       </c>
       <c r="C58" s="3"/>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="4" t="s">
         <v>64</v>
       </c>
       <c r="C59" s="3"/>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="4" t="s">
         <v>65</v>
       </c>
       <c r="C60" s="3"/>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="2" t="s">
+      <c r="A61" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="4" t="s">
         <v>66</v>
       </c>
       <c r="C61" s="3"/>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="2" t="s">
+      <c r="A62" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="4" t="s">
         <v>67</v>
       </c>
       <c r="C62" s="3"/>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C63" s="3"/>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="2" t="s">
+      <c r="A64" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="4" t="s">
         <v>70</v>
       </c>
       <c r="C64" s="3"/>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C65" s="3"/>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66" s="2" t="s">
+      <c r="A66" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="4" t="s">
         <v>72</v>
       </c>
       <c r="C66" s="3"/>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="2" t="s">
+      <c r="A67" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C67" s="3"/>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="2" t="s">
+      <c r="A68" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="4" t="s">
         <v>74</v>
       </c>
       <c r="C68" s="3"/>
     </row>
     <row r="69" spans="1:3">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="4" t="s">
         <v>75</v>
       </c>
       <c r="C69" s="3"/>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70" s="2" t="s">
+      <c r="A70" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="4" t="s">
         <v>76</v>
       </c>
       <c r="C70" s="3"/>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="2" t="s">
+      <c r="A71" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="4" t="s">
         <v>77</v>
       </c>
       <c r="C71" s="3"/>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="2" t="s">
+      <c r="A72" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C72" s="3"/>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="2" t="s">
+      <c r="A73" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="4" t="s">
         <v>80</v>
       </c>
       <c r="C73" s="3"/>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74" s="2" t="s">
+      <c r="A74" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="4" t="s">
         <v>81</v>
       </c>
       <c r="C74" s="3"/>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="2" t="s">
+      <c r="A75" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="4" t="s">
         <v>82</v>
       </c>
       <c r="C75" s="3"/>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="2" t="s">
+      <c r="A76" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" s="4" t="s">
         <v>83</v>
       </c>
       <c r="C76" s="3"/>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C77" s="3"/>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" s="2" t="s">
+      <c r="A78" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C78" s="3"/>
     </row>
     <row r="79" spans="1:3">
-      <c r="A79" s="2" t="s">
+      <c r="A79" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B79" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C79" s="3"/>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="2" t="s">
+      <c r="A80" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" s="4" t="s">
         <v>88</v>
       </c>
       <c r="C80" s="3"/>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="2" t="s">
+      <c r="A81" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B81" s="4" t="s">
         <v>89</v>
       </c>
       <c r="C81" s="3"/>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="2" t="s">
+      <c r="A82" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B82" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C82" s="3"/>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="2" t="s">
+      <c r="A83" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B83" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C83" s="3"/>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="2" t="s">
+      <c r="A84" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B84" s="4" t="s">
         <v>92</v>
       </c>
       <c r="C84" s="3"/>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="2" t="s">
+      <c r="A85" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B85" s="4" t="s">
         <v>93</v>
       </c>
       <c r="C85" s="3"/>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="2" t="s">
+      <c r="A86" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="B86" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C86" s="3"/>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="4" t="s">
+      <c r="A87" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="B87" s="5" t="s">
         <v>95</v>
       </c>
       <c r="C87" s="3"/>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="4" t="s">
+      <c r="A88" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B88" s="4" t="s">
+      <c r="B88" s="5" t="s">
         <v>96</v>
       </c>
       <c r="C88" s="3"/>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="4" t="s">
+      <c r="A89" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B89" s="5" t="s">
         <v>97</v>
       </c>
       <c r="C89" s="3"/>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="2" t="s">
+      <c r="A90" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B90" s="4" t="s">
         <v>99</v>
       </c>
       <c r="C90" s="3"/>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="2" t="s">
+      <c r="A91" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B91" s="4" t="s">
         <v>100</v>
       </c>
       <c r="C91" s="3"/>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="2" t="s">
+      <c r="A92" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B92" s="4" t="s">
         <v>101</v>
       </c>
       <c r="C92" s="3"/>
     </row>
     <row r="93" spans="1:3">
-      <c r="A93" s="2" t="s">
+      <c r="A93" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B93" s="4" t="s">
         <v>102</v>
       </c>
       <c r="C93" s="3"/>
     </row>
     <row r="94" spans="1:3">
-      <c r="A94" s="2" t="s">
+      <c r="A94" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="B94" s="4" t="s">
         <v>103</v>
       </c>
       <c r="C94" s="3"/>
     </row>
     <row r="95" spans="1:3">
-      <c r="A95" s="2" t="s">
+      <c r="A95" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="B95" s="4" t="s">
         <v>105</v>
       </c>
       <c r="C95" s="3"/>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="2" t="s">
+      <c r="A96" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="B96" s="4" t="s">
         <v>106</v>
       </c>
       <c r="C96" s="3"/>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="2" t="s">
+      <c r="A97" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B97" s="5" t="s">
         <v>107</v>
       </c>
       <c r="C97" s="3"/>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98" s="2" t="s">
+      <c r="A98" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B98" s="5" t="s">
         <v>109</v>
       </c>
       <c r="C98" s="3"/>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="2" t="s">
+      <c r="A99" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B99" s="5" t="s">
         <v>110</v>
       </c>
       <c r="C99" s="3"/>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="2" t="s">
+      <c r="A100" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B100" s="5" t="s">
         <v>111</v>
       </c>
       <c r="C100" s="3"/>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101" s="2" t="s">
+      <c r="A101" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B101" s="4" t="s">
+      <c r="B101" s="5" t="s">
         <v>112</v>
       </c>
       <c r="C101" s="3"/>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102" s="2" t="s">
+      <c r="A102" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B102" s="5" t="s">
         <v>113</v>
       </c>
       <c r="C102" s="3"/>
     </row>
     <row r="103" spans="1:3">
-      <c r="A103" s="2" t="s">
+      <c r="A103" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="B103" s="5" t="s">
         <v>114</v>
       </c>
       <c r="C103" s="3"/>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="2" t="s">
+      <c r="A104" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="B104" s="5" t="s">
         <v>116</v>
       </c>
       <c r="C104" s="3"/>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="2" t="s">
+      <c r="A105" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="B105" s="5" t="s">
         <v>117</v>
       </c>
       <c r="C105" s="3"/>
     </row>
     <row r="106" spans="1:3">
-      <c r="A106" s="2" t="s">
+      <c r="A106" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="B106" s="5" t="s">
         <v>118</v>
       </c>
       <c r="C106" s="3"/>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107" s="2" t="s">
+      <c r="A107" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="B107" s="5" t="s">
         <v>120</v>
       </c>
       <c r="C107" s="3"/>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="2" t="s">
+      <c r="A108" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B108" s="5" t="s">
         <v>122</v>
       </c>
       <c r="C108" s="3"/>
     </row>
     <row r="109" spans="1:3">
-      <c r="A109" s="2" t="s">
+      <c r="A109" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B109" s="4" t="s">
+      <c r="B109" s="5" t="s">
         <v>123</v>
       </c>
       <c r="C109" s="3"/>
     </row>
     <row r="110" spans="1:3">
-      <c r="A110" s="2" t="s">
+      <c r="A110" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="B110" s="4" t="s">
         <v>124</v>
       </c>
       <c r="C110" s="3"/>
     </row>
     <row r="111" spans="1:3">
-      <c r="A111" s="2" t="s">
+      <c r="A111" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="B111" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C111" s="3"/>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="2" t="s">
+      <c r="A112" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="B112" s="4" t="s">
         <v>127</v>
       </c>
       <c r="C112" s="3"/>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="2" t="s">
+      <c r="A113" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="B113" s="4" t="s">
         <v>129</v>
       </c>
       <c r="C113" s="3"/>
     </row>
     <row r="114" spans="1:3">
-      <c r="A114" s="2" t="s">
+      <c r="A114" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="B114" s="4" t="s">
         <v>130</v>
       </c>
       <c r="C114" s="3"/>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="2" t="s">
+      <c r="A115" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="B115" s="4" t="s">
         <v>113</v>
       </c>
       <c r="C115" s="3"/>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="2" t="s">
+      <c r="A116" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="B116" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C116" s="3"/>
     </row>
     <row r="117" spans="1:3">
-      <c r="A117" s="2" t="s">
+      <c r="A117" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="B117" s="4" t="s">
         <v>131</v>
       </c>
       <c r="C117" s="3"/>
     </row>
     <row r="118" spans="1:3">
-      <c r="A118" s="2" t="s">
+      <c r="A118" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="B118" s="4" t="s">
         <v>132</v>
       </c>
       <c r="C118" s="3"/>
     </row>
     <row r="119" spans="1:3">
-      <c r="A119" s="2" t="s">
+      <c r="A119" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="B119" s="4" t="s">
         <v>133</v>
       </c>
       <c r="C119" s="3"/>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="2" t="s">
+      <c r="A120" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="B120" s="4" t="s">
         <v>134</v>
       </c>
       <c r="C120" s="3"/>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="2" t="s">
+      <c r="A121" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="B121" s="4" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="122" spans="1:3">
-      <c r="A122" s="2" t="s">
+      <c r="A122" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="B122" s="4" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="2" t="s">
+      <c r="A123" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="B123" s="4" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="2" t="s">
+      <c r="A124" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="B124" s="4" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="125" spans="1:3">
-      <c r="A125" s="2" t="s">
+      <c r="A125" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="B125" s="4" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="126" spans="1:3">
-      <c r="A126" s="2" t="s">
+      <c r="A126" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="B126" s="4" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="127" spans="1:3">
-      <c r="A127" s="2" t="s">
+      <c r="A127" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="B127" s="4" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="2" t="s">
+      <c r="A128" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="B128" s="4" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="2" t="s">
+      <c r="A129" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="B129" s="4" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="130" spans="1:2">
-      <c r="A130" s="1" t="s">
+      <c r="A130" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B130" s="1" t="s">
+      <c r="B130" s="4" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="2" t="s">
+      <c r="A131" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="B131" s="4" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="132" spans="1:2">
-      <c r="A132" s="2" t="s">
+      <c r="A132" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="B132" s="4" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="1" t="s">
+      <c r="A133" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="B133" s="4" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="1" t="s">
+      <c r="A134" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="B134" s="4" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="2" t="s">
+      <c r="A135" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="B135" s="4" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="2" t="s">
+      <c r="A136" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="B136" s="4" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="2" t="s">
+      <c r="A137" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="B137" s="4" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="2" t="s">
+      <c r="A138" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="B138" s="4" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="2" t="s">
+      <c r="A139" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="B139" s="4" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="2" t="s">
+      <c r="A140" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="B140" s="4" t="s">
         <v>154</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="158">
   <si>
     <t>UA名字</t>
   </si>
@@ -1148,16 +1148,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1482,7 +1479,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C145"/>
+  <dimension ref="A1:C144"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -1498,1274 +1495,1266 @@
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="3"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="3"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="3"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="3"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="3"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C19" s="3"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C20" s="3"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C21" s="3"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="3"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="3"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C24" s="3"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C25" s="3"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C26" s="3"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="3"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C30" s="3"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C31" s="3"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C32" s="3"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C33" s="3"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C34" s="3"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C35" s="3"/>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C36" s="3"/>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C37" s="3"/>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C38" s="3"/>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C39" s="3"/>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C40" s="3"/>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C41" s="3"/>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C42" s="3"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C43" s="3"/>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C44" s="3"/>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C45" s="3"/>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C46" s="3"/>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C47" s="3"/>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C48" s="3"/>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C49" s="3"/>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C50" s="3"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C51" s="3"/>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C52" s="3"/>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C53" s="3"/>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C54" s="3"/>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C55" s="3"/>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C56" s="3"/>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C57" s="3"/>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C58" s="3"/>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C59" s="3"/>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C60" s="3"/>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C61" s="3"/>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C62" s="3"/>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C63" s="3"/>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C64" s="3"/>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C65" s="3"/>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C66" s="3"/>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C67" s="3"/>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C68" s="3"/>
     </row>
     <row r="69" spans="1:3">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C69" s="3"/>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70" s="4" t="s">
+      <c r="A70" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C70" s="3"/>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="4" t="s">
+      <c r="A71" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C71" s="3"/>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C72" s="3"/>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="4" t="s">
+      <c r="A73" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C73" s="3"/>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C74" s="3"/>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="4" t="s">
+      <c r="A75" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C75" s="3"/>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C76" s="3"/>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="4" t="s">
+      <c r="A77" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B77" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C77" s="3"/>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" s="4" t="s">
+      <c r="A78" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B78" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C78" s="3"/>
     </row>
     <row r="79" spans="1:3">
-      <c r="A79" s="4" t="s">
+      <c r="A79" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="B79" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C79" s="3"/>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="4" t="s">
+      <c r="A80" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B80" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C80" s="3"/>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="4" t="s">
+      <c r="A81" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="B81" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C81" s="3"/>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="4" t="s">
+      <c r="A82" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B82" s="4" t="s">
+      <c r="B82" s="2" t="s">
         <v>90</v>
       </c>
       <c r="C82" s="3"/>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="4" t="s">
+      <c r="A83" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="B83" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C83" s="3"/>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="4" t="s">
+      <c r="A84" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B84" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C84" s="3"/>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="4" t="s">
+      <c r="A85" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C85" s="3"/>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="4" t="s">
+      <c r="A86" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C86" s="3"/>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="5" t="s">
+      <c r="A87" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="B87" s="4" t="s">
         <v>95</v>
       </c>
       <c r="C87" s="3"/>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="5" t="s">
+      <c r="A88" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B88" s="5" t="s">
+      <c r="B88" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C88" s="3"/>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="5" t="s">
+      <c r="A89" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B89" s="5" t="s">
+      <c r="B89" s="4" t="s">
         <v>97</v>
       </c>
       <c r="C89" s="3"/>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="4" t="s">
+      <c r="A90" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="B90" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C90" s="3"/>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="4" t="s">
+      <c r="A91" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C91" s="3"/>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="4" t="s">
+      <c r="A92" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B92" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C92" s="3"/>
     </row>
     <row r="93" spans="1:3">
-      <c r="A93" s="4" t="s">
+      <c r="A93" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B93" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C93" s="3"/>
     </row>
     <row r="94" spans="1:3">
-      <c r="A94" s="4" t="s">
+      <c r="A94" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B94" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C94" s="3"/>
     </row>
     <row r="95" spans="1:3">
-      <c r="A95" s="4" t="s">
+      <c r="A95" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B95" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C95" s="3"/>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="4" t="s">
+      <c r="A96" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B96" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C96" s="3"/>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="4" t="s">
+      <c r="A97" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B97" s="5" t="s">
+      <c r="B97" s="4" t="s">
         <v>107</v>
       </c>
       <c r="C97" s="3"/>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98" s="4" t="s">
+      <c r="A98" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B98" s="5" t="s">
+      <c r="B98" s="4" t="s">
         <v>109</v>
       </c>
       <c r="C98" s="3"/>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="4" t="s">
+      <c r="A99" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B99" s="5" t="s">
+      <c r="B99" s="4" t="s">
         <v>110</v>
       </c>
       <c r="C99" s="3"/>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="4" t="s">
+      <c r="A100" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B100" s="5" t="s">
+      <c r="B100" s="4" t="s">
         <v>111</v>
       </c>
       <c r="C100" s="3"/>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101" s="4" t="s">
+      <c r="A101" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B101" s="5" t="s">
+      <c r="B101" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C101" s="3"/>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102" s="4" t="s">
+      <c r="A102" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B102" s="5" t="s">
+      <c r="B102" s="4" t="s">
         <v>113</v>
       </c>
       <c r="C102" s="3"/>
     </row>
     <row r="103" spans="1:3">
-      <c r="A103" s="4" t="s">
+      <c r="A103" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B103" s="5" t="s">
+      <c r="B103" s="4" t="s">
         <v>114</v>
       </c>
       <c r="C103" s="3"/>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="4" t="s">
+      <c r="A104" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B104" s="5" t="s">
+      <c r="B104" s="4" t="s">
         <v>116</v>
       </c>
       <c r="C104" s="3"/>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="4" t="s">
+      <c r="A105" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B105" s="5" t="s">
+      <c r="B105" s="4" t="s">
         <v>117</v>
       </c>
       <c r="C105" s="3"/>
     </row>
     <row r="106" spans="1:3">
-      <c r="A106" s="4" t="s">
+      <c r="A106" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B106" s="5" t="s">
+      <c r="B106" s="4" t="s">
         <v>118</v>
       </c>
       <c r="C106" s="3"/>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107" s="4" t="s">
+      <c r="A107" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B107" s="5" t="s">
+      <c r="B107" s="4" t="s">
         <v>120</v>
       </c>
       <c r="C107" s="3"/>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="4" t="s">
+      <c r="A108" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B108" s="5" t="s">
+      <c r="B108" s="4" t="s">
         <v>122</v>
       </c>
       <c r="C108" s="3"/>
     </row>
     <row r="109" spans="1:3">
-      <c r="A109" s="4" t="s">
+      <c r="A109" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B109" s="5" t="s">
+      <c r="B109" s="4" t="s">
         <v>123</v>
       </c>
       <c r="C109" s="3"/>
     </row>
     <row r="110" spans="1:3">
-      <c r="A110" s="4" t="s">
+      <c r="A110" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B110" s="4" t="s">
+      <c r="B110" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C110" s="3"/>
     </row>
     <row r="111" spans="1:3">
-      <c r="A111" s="4" t="s">
+      <c r="A111" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B111" s="4" t="s">
+      <c r="B111" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C111" s="3"/>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="4" t="s">
+      <c r="A112" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B112" s="4" t="s">
+      <c r="B112" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C112" s="3"/>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="4" t="s">
+      <c r="A113" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B113" s="4" t="s">
+      <c r="B113" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C113" s="3"/>
     </row>
     <row r="114" spans="1:3">
-      <c r="A114" s="4" t="s">
+      <c r="A114" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B114" s="4" t="s">
+      <c r="B114" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C114" s="3"/>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="4" t="s">
+      <c r="A115" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B115" s="4" t="s">
+      <c r="B115" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C115" s="3"/>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="4" t="s">
+      <c r="A116" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B116" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C116" s="3"/>
     </row>
     <row r="117" spans="1:3">
-      <c r="A117" s="4" t="s">
+      <c r="A117" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="B117" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C117" s="3"/>
     </row>
     <row r="118" spans="1:3">
-      <c r="A118" s="4" t="s">
+      <c r="A118" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B118" s="4" t="s">
+      <c r="B118" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C118" s="3"/>
     </row>
     <row r="119" spans="1:3">
-      <c r="A119" s="4" t="s">
+      <c r="A119" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B119" s="4" t="s">
+      <c r="B119" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C119" s="3"/>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="4" t="s">
+      <c r="A120" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B120" s="4" t="s">
+      <c r="B120" s="2" t="s">
         <v>134</v>
       </c>
       <c r="C120" s="3"/>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="4" t="s">
+      <c r="A121" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B121" s="4" t="s">
+      <c r="B121" s="2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="122" spans="1:3">
-      <c r="A122" s="4" t="s">
+      <c r="A122" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B122" s="4" t="s">
+      <c r="B122" s="2" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="4" t="s">
+      <c r="A123" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B123" s="4" t="s">
+      <c r="B123" s="2" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="4" t="s">
+      <c r="A124" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B124" s="4" t="s">
+      <c r="B124" s="2" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="125" spans="1:3">
-      <c r="A125" s="4" t="s">
+      <c r="A125" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B125" s="4" t="s">
+      <c r="B125" s="2" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="126" spans="1:3">
-      <c r="A126" s="4" t="s">
+      <c r="A126" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B126" s="4" t="s">
+      <c r="B126" s="2" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="127" spans="1:3">
-      <c r="A127" s="4" t="s">
+      <c r="A127" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B127" s="4" t="s">
+      <c r="B127" s="2" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="4" t="s">
+      <c r="A128" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B128" s="4" t="s">
+      <c r="B128" s="2" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="4" t="s">
+      <c r="A129" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B129" s="4" t="s">
+      <c r="B129" s="2" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="130" spans="1:2">
-      <c r="A130" s="4" t="s">
+      <c r="A130" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B130" s="4" t="s">
+      <c r="B130" s="2" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="4" t="s">
+      <c r="A131" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B131" s="4" t="s">
+      <c r="B131" s="2" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="132" spans="1:2">
-      <c r="A132" s="4" t="s">
+      <c r="A132" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B132" s="4" t="s">
+      <c r="B132" s="2" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="4" t="s">
+      <c r="A133" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B133" s="4" t="s">
+      <c r="B133" s="2" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="4" t="s">
+      <c r="A134" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B134" s="4" t="s">
+      <c r="B134" s="2" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="4" t="s">
+      <c r="A135" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B135" s="4" t="s">
+      <c r="B135" s="2" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="4" t="s">
+      <c r="A136" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B136" s="4" t="s">
+      <c r="B136" s="2" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="4" t="s">
+      <c r="A137" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B137" s="4" t="s">
+      <c r="B137" s="2" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="4" t="s">
+      <c r="A138" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B138" s="4" t="s">
+      <c r="B138" s="2" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="4" t="s">
+      <c r="A139" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B139" s="4" t="s">
+      <c r="B139" s="2" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="4" t="s">
+      <c r="A140" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B140" s="4" t="s">
+      <c r="B140" s="2" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="4" t="s">
+      <c r="A141" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B141" s="4" t="s">
+      <c r="B141" s="2" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="4" t="s">
+      <c r="A142" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B142" s="4" t="s">
+      <c r="B142" s="2" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="4" t="s">
+      <c r="A143" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B143" s="4" t="s">
+      <c r="B143" s="2" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="4" t="s">
+      <c r="A144" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B144" s="4" t="s">
+      <c r="B144" s="2" t="s">
         <v>157</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2">
-      <c r="A145" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B145" s="4" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="158">
   <si>
     <t>UA名字</t>
   </si>
@@ -1479,7 +1479,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C144"/>
+  <dimension ref="A1:C143"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -2746,14 +2746,6 @@
         <v>28</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2">
-      <c r="A144" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B144" s="2" t="s">
         <v>157</v>
       </c>
     </row>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="159">
   <si>
     <t>UA名字</t>
   </si>
@@ -506,6 +506,9 @@
   </si>
   <si>
     <t>9418</t>
+  </si>
+  <si>
+    <t>8430</t>
   </si>
 </sst>
 </file>
@@ -1148,7 +1151,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1158,6 +1161,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1479,7 +1485,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C143"/>
+  <dimension ref="A1:C144"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -2749,6 +2755,14 @@
         <v>157</v>
       </c>
     </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="160">
   <si>
     <t>UA名字</t>
   </si>
@@ -509,6 +509,9 @@
   </si>
   <si>
     <t>8430</t>
+  </si>
+  <si>
+    <t>5349</t>
   </si>
 </sst>
 </file>
@@ -1151,7 +1154,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1161,9 +1164,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1485,7 +1485,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C144"/>
+  <dimension ref="A1:C145"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -2756,11 +2756,19 @@
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="5" t="s">
+      <c r="A144" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B144" s="5" t="s">
+      <c r="B144" s="2" t="s">
         <v>158</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="162">
   <si>
     <t>UA名字</t>
   </si>
@@ -512,6 +512,12 @@
   </si>
   <si>
     <t>5349</t>
+  </si>
+  <si>
+    <t>3065</t>
+  </si>
+  <si>
+    <t>3240</t>
   </si>
 </sst>
 </file>
@@ -1154,7 +1160,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1164,6 +1170,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1485,7 +1494,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C145"/>
+  <dimension ref="A1:C147"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -2771,6 +2780,22 @@
         <v>159</v>
       </c>
     </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="171">
   <si>
     <t>UA名字</t>
   </si>
@@ -518,6 +518,33 @@
   </si>
   <si>
     <t>3240</t>
+  </si>
+  <si>
+    <t>8818</t>
+  </si>
+  <si>
+    <t>4513</t>
+  </si>
+  <si>
+    <t>1895</t>
+  </si>
+  <si>
+    <t>8667</t>
+  </si>
+  <si>
+    <t>7295</t>
+  </si>
+  <si>
+    <t>8694</t>
+  </si>
+  <si>
+    <t>7860</t>
+  </si>
+  <si>
+    <t>6465</t>
+  </si>
+  <si>
+    <t>7617</t>
   </si>
 </sst>
 </file>
@@ -1494,7 +1521,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C147"/>
+  <dimension ref="A1:C156"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -2781,19 +2808,91 @@
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="5" t="s">
+      <c r="A146" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B146" s="5" t="s">
+      <c r="B146" s="2" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="5" t="s">
+      <c r="A147" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B147" s="5" t="s">
+      <c r="B147" s="2" t="s">
         <v>161</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="176">
   <si>
     <t>UA名字</t>
   </si>
@@ -545,6 +545,21 @@
   </si>
   <si>
     <t>7617</t>
+  </si>
+  <si>
+    <t>3305</t>
+  </si>
+  <si>
+    <t>9376</t>
+  </si>
+  <si>
+    <t>3933</t>
+  </si>
+  <si>
+    <t>3631</t>
+  </si>
+  <si>
+    <t>9912</t>
   </si>
 </sst>
 </file>
@@ -1521,7 +1536,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C156"/>
+  <dimension ref="A1:C161"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -2824,75 +2839,115 @@
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="5" t="s">
+      <c r="A148" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B148" s="5" t="s">
+      <c r="B148" s="2" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="5" t="s">
+      <c r="A149" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B149" s="5" t="s">
+      <c r="B149" s="2" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="5" t="s">
+      <c r="A150" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B150" s="5" t="s">
+      <c r="B150" s="2" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="5" t="s">
+      <c r="A151" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B151" s="5" t="s">
+      <c r="B151" s="2" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="5" t="s">
+      <c r="A152" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B152" s="5" t="s">
+      <c r="B152" s="2" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="5" t="s">
+      <c r="A153" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B153" s="5" t="s">
+      <c r="B153" s="2" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="5" t="s">
+      <c r="A154" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B154" s="5" t="s">
+      <c r="B154" s="2" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="5" t="s">
+      <c r="A155" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B155" s="5" t="s">
+      <c r="B155" s="2" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="5" t="s">
+      <c r="A156" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B156" s="5" t="s">
+      <c r="B156" s="2" t="s">
         <v>170</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="179">
   <si>
     <t>UA名字</t>
   </si>
@@ -560,6 +560,15 @@
   </si>
   <si>
     <t>9912</t>
+  </si>
+  <si>
+    <t>7324</t>
+  </si>
+  <si>
+    <t>3220</t>
+  </si>
+  <si>
+    <t>9179</t>
   </si>
 </sst>
 </file>
@@ -1536,7 +1545,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C161"/>
+  <dimension ref="A1:C164"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -2911,43 +2920,67 @@
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="5" t="s">
+      <c r="A157" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B157" s="5" t="s">
+      <c r="B157" s="2" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="5" t="s">
+      <c r="A158" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B158" s="5" t="s">
+      <c r="B158" s="2" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="5" t="s">
+      <c r="A159" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B159" s="5" t="s">
+      <c r="B159" s="2" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="5" t="s">
+      <c r="A160" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B160" s="5" t="s">
+      <c r="B160" s="2" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="5" t="s">
+      <c r="A161" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B161" s="5" t="s">
+      <c r="B161" s="2" t="s">
         <v>175</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="180">
   <si>
     <t>UA名字</t>
   </si>
@@ -569,6 +569,9 @@
   </si>
   <si>
     <t>9179</t>
+  </si>
+  <si>
+    <t>3239</t>
   </si>
 </sst>
 </file>
@@ -1545,7 +1548,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C164"/>
+  <dimension ref="A1:C165"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -2960,27 +2963,35 @@
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="5" t="s">
+      <c r="A162" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B162" s="5" t="s">
+      <c r="B162" s="2" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="5" t="s">
+      <c r="A163" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B163" s="5" t="s">
+      <c r="B163" s="2" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="5" t="s">
+      <c r="A164" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B164" s="5" t="s">
+      <c r="B164" s="2" t="s">
         <v>178</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="182">
   <si>
     <t>UA名字</t>
   </si>
@@ -572,6 +572,12 @@
   </si>
   <si>
     <t>3239</t>
+  </si>
+  <si>
+    <t>5583</t>
+  </si>
+  <si>
+    <t>2950</t>
   </si>
 </sst>
 </file>
@@ -1548,7 +1554,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C165"/>
+  <dimension ref="A1:C167"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -2987,11 +2993,27 @@
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="5" t="s">
+      <c r="A165" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B165" s="5" t="s">
+      <c r="B165" s="2" t="s">
         <v>179</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="188">
   <si>
     <t>UA名字</t>
   </si>
@@ -578,6 +578,24 @@
   </si>
   <si>
     <t>2950</t>
+  </si>
+  <si>
+    <t>5543</t>
+  </si>
+  <si>
+    <t>5427</t>
+  </si>
+  <si>
+    <t>3465</t>
+  </si>
+  <si>
+    <t>1783</t>
+  </si>
+  <si>
+    <t>7777</t>
+  </si>
+  <si>
+    <t>2498</t>
   </si>
 </sst>
 </file>
@@ -1554,7 +1572,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C167"/>
+  <dimension ref="A1:C173"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3001,19 +3019,67 @@
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="5" t="s">
+      <c r="A166" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B166" s="5" t="s">
+      <c r="B166" s="2" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="5" t="s">
+      <c r="A167" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B167" s="5" t="s">
+      <c r="B167" s="2" t="s">
         <v>181</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="189">
   <si>
     <t>UA名字</t>
   </si>
@@ -596,6 +596,9 @@
   </si>
   <si>
     <t>2498</t>
+  </si>
+  <si>
+    <t>4743</t>
   </si>
 </sst>
 </file>
@@ -1572,7 +1575,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C173"/>
+  <dimension ref="A1:C174"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3035,51 +3038,59 @@
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="5" t="s">
+      <c r="A168" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B168" s="5" t="s">
+      <c r="B168" s="2" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="5" t="s">
+      <c r="A169" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B169" s="5" t="s">
+      <c r="B169" s="2" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="5" t="s">
+      <c r="A170" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B170" s="5" t="s">
+      <c r="B170" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="5" t="s">
+      <c r="A171" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B171" s="5" t="s">
+      <c r="B171" s="2" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="5" t="s">
+      <c r="A172" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B172" s="5" t="s">
+      <c r="B172" s="2" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="5" t="s">
+      <c r="A173" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B173" s="5" t="s">
+      <c r="B173" s="2" t="s">
         <v>187</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="195">
   <si>
     <t>UA名字</t>
   </si>
@@ -599,6 +599,24 @@
   </si>
   <si>
     <t>4743</t>
+  </si>
+  <si>
+    <t>4860</t>
+  </si>
+  <si>
+    <t>4829</t>
+  </si>
+  <si>
+    <t>3749</t>
+  </si>
+  <si>
+    <t>4240</t>
+  </si>
+  <si>
+    <t>0965</t>
+  </si>
+  <si>
+    <t>7840</t>
   </si>
 </sst>
 </file>
@@ -1575,7 +1593,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C174"/>
+  <dimension ref="A1:C180"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3086,11 +3104,59 @@
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="5" t="s">
+      <c r="A174" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B174" s="5" t="s">
+      <c r="B174" s="2" t="s">
         <v>188</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="194">
   <si>
     <t>UA名字</t>
   </si>
@@ -605,9 +605,6 @@
   </si>
   <si>
     <t>4829</t>
-  </si>
-  <si>
-    <t>3749</t>
   </si>
   <si>
     <t>4240</t>
@@ -1268,10 +1265,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1609,1555 +1606,1551 @@
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="3"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="3"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="3"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="3"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="3"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C19" s="3"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C20" s="3"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C21" s="3"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="3"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="3"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C24" s="3"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C25" s="3"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C26" s="3"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="3"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C30" s="3"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C31" s="3"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C32" s="3"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C33" s="3"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C34" s="3"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C35" s="3"/>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C36" s="3"/>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C37" s="3"/>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C38" s="3"/>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C39" s="3"/>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C40" s="3"/>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="4" t="s">
         <v>44</v>
       </c>
       <c r="C41" s="3"/>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C42" s="3"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C43" s="3"/>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="4" t="s">
         <v>48</v>
       </c>
       <c r="C44" s="3"/>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="4" t="s">
         <v>49</v>
       </c>
       <c r="C45" s="3"/>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C46" s="3"/>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C47" s="3"/>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C48" s="3"/>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="4" t="s">
         <v>53</v>
       </c>
       <c r="C49" s="3"/>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="4" t="s">
         <v>54</v>
       </c>
       <c r="C50" s="3"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="4" t="s">
         <v>55</v>
       </c>
       <c r="C51" s="3"/>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="4" t="s">
         <v>57</v>
       </c>
       <c r="C52" s="3"/>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="4" t="s">
         <v>58</v>
       </c>
       <c r="C53" s="3"/>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="4" t="s">
         <v>59</v>
       </c>
       <c r="C54" s="3"/>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="4" t="s">
         <v>60</v>
       </c>
       <c r="C55" s="3"/>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="4" t="s">
         <v>61</v>
       </c>
       <c r="C56" s="3"/>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="4" t="s">
         <v>62</v>
       </c>
       <c r="C57" s="3"/>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="4" t="s">
         <v>63</v>
       </c>
       <c r="C58" s="3"/>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="4" t="s">
         <v>64</v>
       </c>
       <c r="C59" s="3"/>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="4" t="s">
         <v>65</v>
       </c>
       <c r="C60" s="3"/>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="2" t="s">
+      <c r="A61" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="4" t="s">
         <v>66</v>
       </c>
       <c r="C61" s="3"/>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="2" t="s">
+      <c r="A62" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="4" t="s">
         <v>67</v>
       </c>
       <c r="C62" s="3"/>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C63" s="3"/>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="2" t="s">
+      <c r="A64" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="4" t="s">
         <v>70</v>
       </c>
       <c r="C64" s="3"/>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C65" s="3"/>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66" s="2" t="s">
+      <c r="A66" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="4" t="s">
         <v>72</v>
       </c>
       <c r="C66" s="3"/>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="2" t="s">
+      <c r="A67" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C67" s="3"/>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="2" t="s">
+      <c r="A68" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="4" t="s">
         <v>74</v>
       </c>
       <c r="C68" s="3"/>
     </row>
     <row r="69" spans="1:3">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="4" t="s">
         <v>75</v>
       </c>
       <c r="C69" s="3"/>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70" s="2" t="s">
+      <c r="A70" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="4" t="s">
         <v>76</v>
       </c>
       <c r="C70" s="3"/>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="2" t="s">
+      <c r="A71" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="4" t="s">
         <v>77</v>
       </c>
       <c r="C71" s="3"/>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="2" t="s">
+      <c r="A72" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C72" s="3"/>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="2" t="s">
+      <c r="A73" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="4" t="s">
         <v>80</v>
       </c>
       <c r="C73" s="3"/>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74" s="2" t="s">
+      <c r="A74" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="4" t="s">
         <v>81</v>
       </c>
       <c r="C74" s="3"/>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="2" t="s">
+      <c r="A75" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="4" t="s">
         <v>82</v>
       </c>
       <c r="C75" s="3"/>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="2" t="s">
+      <c r="A76" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" s="4" t="s">
         <v>83</v>
       </c>
       <c r="C76" s="3"/>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C77" s="3"/>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" s="2" t="s">
+      <c r="A78" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C78" s="3"/>
     </row>
     <row r="79" spans="1:3">
-      <c r="A79" s="2" t="s">
+      <c r="A79" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B79" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C79" s="3"/>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="2" t="s">
+      <c r="A80" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" s="4" t="s">
         <v>88</v>
       </c>
       <c r="C80" s="3"/>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="2" t="s">
+      <c r="A81" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B81" s="4" t="s">
         <v>89</v>
       </c>
       <c r="C81" s="3"/>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="2" t="s">
+      <c r="A82" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B82" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C82" s="3"/>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="2" t="s">
+      <c r="A83" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B83" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C83" s="3"/>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="2" t="s">
+      <c r="A84" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B84" s="4" t="s">
         <v>92</v>
       </c>
       <c r="C84" s="3"/>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="2" t="s">
+      <c r="A85" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B85" s="4" t="s">
         <v>93</v>
       </c>
       <c r="C85" s="3"/>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="2" t="s">
+      <c r="A86" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="B86" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C86" s="3"/>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="4" t="s">
+      <c r="A87" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="B87" s="5" t="s">
         <v>95</v>
       </c>
       <c r="C87" s="3"/>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="4" t="s">
+      <c r="A88" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B88" s="4" t="s">
+      <c r="B88" s="5" t="s">
         <v>96</v>
       </c>
       <c r="C88" s="3"/>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="4" t="s">
+      <c r="A89" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B89" s="5" t="s">
         <v>97</v>
       </c>
       <c r="C89" s="3"/>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="2" t="s">
+      <c r="A90" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B90" s="4" t="s">
         <v>99</v>
       </c>
       <c r="C90" s="3"/>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="2" t="s">
+      <c r="A91" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B91" s="4" t="s">
         <v>100</v>
       </c>
       <c r="C91" s="3"/>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="2" t="s">
+      <c r="A92" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B92" s="4" t="s">
         <v>101</v>
       </c>
       <c r="C92" s="3"/>
     </row>
     <row r="93" spans="1:3">
-      <c r="A93" s="2" t="s">
+      <c r="A93" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B93" s="4" t="s">
         <v>102</v>
       </c>
       <c r="C93" s="3"/>
     </row>
     <row r="94" spans="1:3">
-      <c r="A94" s="2" t="s">
+      <c r="A94" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="B94" s="4" t="s">
         <v>103</v>
       </c>
       <c r="C94" s="3"/>
     </row>
     <row r="95" spans="1:3">
-      <c r="A95" s="2" t="s">
+      <c r="A95" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="B95" s="4" t="s">
         <v>105</v>
       </c>
       <c r="C95" s="3"/>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="2" t="s">
+      <c r="A96" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="B96" s="4" t="s">
         <v>106</v>
       </c>
       <c r="C96" s="3"/>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="2" t="s">
+      <c r="A97" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B97" s="5" t="s">
         <v>107</v>
       </c>
       <c r="C97" s="3"/>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98" s="2" t="s">
+      <c r="A98" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B98" s="5" t="s">
         <v>109</v>
       </c>
       <c r="C98" s="3"/>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="2" t="s">
+      <c r="A99" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B99" s="5" t="s">
         <v>110</v>
       </c>
       <c r="C99" s="3"/>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="2" t="s">
+      <c r="A100" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B100" s="5" t="s">
         <v>111</v>
       </c>
       <c r="C100" s="3"/>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101" s="2" t="s">
+      <c r="A101" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B101" s="4" t="s">
+      <c r="B101" s="5" t="s">
         <v>112</v>
       </c>
       <c r="C101" s="3"/>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102" s="2" t="s">
+      <c r="A102" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B102" s="5" t="s">
         <v>113</v>
       </c>
       <c r="C102" s="3"/>
     </row>
     <row r="103" spans="1:3">
-      <c r="A103" s="2" t="s">
+      <c r="A103" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="B103" s="5" t="s">
         <v>114</v>
       </c>
       <c r="C103" s="3"/>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="2" t="s">
+      <c r="A104" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="B104" s="5" t="s">
         <v>116</v>
       </c>
       <c r="C104" s="3"/>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="2" t="s">
+      <c r="A105" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="B105" s="5" t="s">
         <v>117</v>
       </c>
       <c r="C105" s="3"/>
     </row>
     <row r="106" spans="1:3">
-      <c r="A106" s="2" t="s">
+      <c r="A106" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="B106" s="5" t="s">
         <v>118</v>
       </c>
       <c r="C106" s="3"/>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107" s="2" t="s">
+      <c r="A107" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="B107" s="5" t="s">
         <v>120</v>
       </c>
       <c r="C107" s="3"/>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="2" t="s">
+      <c r="A108" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B108" s="5" t="s">
         <v>122</v>
       </c>
       <c r="C108" s="3"/>
     </row>
     <row r="109" spans="1:3">
-      <c r="A109" s="2" t="s">
+      <c r="A109" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B109" s="4" t="s">
+      <c r="B109" s="5" t="s">
         <v>123</v>
       </c>
       <c r="C109" s="3"/>
     </row>
     <row r="110" spans="1:3">
-      <c r="A110" s="2" t="s">
+      <c r="A110" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="B110" s="4" t="s">
         <v>124</v>
       </c>
       <c r="C110" s="3"/>
     </row>
     <row r="111" spans="1:3">
-      <c r="A111" s="2" t="s">
+      <c r="A111" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="B111" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C111" s="3"/>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="2" t="s">
+      <c r="A112" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="B112" s="4" t="s">
         <v>127</v>
       </c>
       <c r="C112" s="3"/>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="2" t="s">
+      <c r="A113" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="B113" s="4" t="s">
         <v>129</v>
       </c>
       <c r="C113" s="3"/>
     </row>
     <row r="114" spans="1:3">
-      <c r="A114" s="2" t="s">
+      <c r="A114" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="B114" s="4" t="s">
         <v>130</v>
       </c>
       <c r="C114" s="3"/>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="2" t="s">
+      <c r="A115" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="B115" s="4" t="s">
         <v>113</v>
       </c>
       <c r="C115" s="3"/>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="2" t="s">
+      <c r="A116" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="B116" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C116" s="3"/>
     </row>
     <row r="117" spans="1:3">
-      <c r="A117" s="2" t="s">
+      <c r="A117" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="B117" s="4" t="s">
         <v>131</v>
       </c>
       <c r="C117" s="3"/>
     </row>
     <row r="118" spans="1:3">
-      <c r="A118" s="2" t="s">
+      <c r="A118" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="B118" s="4" t="s">
         <v>132</v>
       </c>
       <c r="C118" s="3"/>
     </row>
     <row r="119" spans="1:3">
-      <c r="A119" s="2" t="s">
+      <c r="A119" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="B119" s="4" t="s">
         <v>133</v>
       </c>
       <c r="C119" s="3"/>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="2" t="s">
+      <c r="A120" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="B120" s="4" t="s">
         <v>134</v>
       </c>
       <c r="C120" s="3"/>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="2" t="s">
+      <c r="A121" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="B121" s="4" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="122" spans="1:3">
-      <c r="A122" s="2" t="s">
+      <c r="A122" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="B122" s="4" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="2" t="s">
+      <c r="A123" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="B123" s="4" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="2" t="s">
+      <c r="A124" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="B124" s="4" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="125" spans="1:3">
-      <c r="A125" s="2" t="s">
+      <c r="A125" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="B125" s="4" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="126" spans="1:3">
-      <c r="A126" s="2" t="s">
+      <c r="A126" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="B126" s="4" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="127" spans="1:3">
-      <c r="A127" s="2" t="s">
+      <c r="A127" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="B127" s="4" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="2" t="s">
+      <c r="A128" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="B128" s="4" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="2" t="s">
+      <c r="A129" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="B129" s="4" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="130" spans="1:2">
-      <c r="A130" s="2" t="s">
+      <c r="A130" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="B130" s="4" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="2" t="s">
+      <c r="A131" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="B131" s="4" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="132" spans="1:2">
-      <c r="A132" s="2" t="s">
+      <c r="A132" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="B132" s="4" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="2" t="s">
+      <c r="A133" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="B133" s="4" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="2" t="s">
+      <c r="A134" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="B134" s="4" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="2" t="s">
+      <c r="A135" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="B135" s="4" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="2" t="s">
+      <c r="A136" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="B136" s="4" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="2" t="s">
+      <c r="A137" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="B137" s="4" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="2" t="s">
+      <c r="A138" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="B138" s="4" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="2" t="s">
+      <c r="A139" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="B139" s="4" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="2" t="s">
+      <c r="A140" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="B140" s="4" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="2" t="s">
+      <c r="A141" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="B141" s="4" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="2" t="s">
+      <c r="A142" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B142" s="2" t="s">
+      <c r="B142" s="4" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="2" t="s">
+      <c r="A143" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B143" s="2" t="s">
+      <c r="B143" s="4" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="2" t="s">
+      <c r="A144" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B144" s="2" t="s">
+      <c r="B144" s="4" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="1" t="s">
+      <c r="A145" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B145" s="1" t="s">
+      <c r="B145" s="4" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="2" t="s">
+      <c r="A146" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B146" s="2" t="s">
+      <c r="B146" s="4" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="2" t="s">
+      <c r="A147" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B147" s="2" t="s">
+      <c r="B147" s="4" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="2" t="s">
+      <c r="A148" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B148" s="2" t="s">
+      <c r="B148" s="4" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="2" t="s">
+      <c r="A149" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B149" s="2" t="s">
+      <c r="B149" s="4" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="2" t="s">
+      <c r="A150" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B150" s="2" t="s">
+      <c r="B150" s="4" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="2" t="s">
+      <c r="A151" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B151" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2">
-      <c r="A152" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2">
-      <c r="A153" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2">
-      <c r="A154" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2">
-      <c r="A155" s="2" t="s">
+      <c r="B177" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B155" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2">
-      <c r="A156" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2">
-      <c r="A157" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2">
-      <c r="A158" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2">
-      <c r="A159" s="2" t="s">
+      <c r="B178" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B159" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2">
-      <c r="A160" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2">
-      <c r="A161" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B161" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2">
-      <c r="A162" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2">
-      <c r="A163" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2">
-      <c r="A164" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2">
-      <c r="A165" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B165" s="2" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2">
-      <c r="A166" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B166" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2">
-      <c r="A167" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2">
-      <c r="A168" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2">
-      <c r="A169" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2">
-      <c r="A170" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B170" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2">
-      <c r="A171" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B171" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2">
-      <c r="A172" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B172" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2">
-      <c r="A173" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2">
-      <c r="A174" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2">
-      <c r="A175" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="B175" s="5" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2">
-      <c r="A176" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B176" s="5" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2">
-      <c r="A177" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B177" s="5" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2">
-      <c r="A178" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="B178" s="5" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2">
-      <c r="A179" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="B179" s="5" t="s">
+      <c r="B179" s="4" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B180" s="5" t="s">
-        <v>194</v>
-      </c>
+      <c r="A180" s="2"/>
+      <c r="B180" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="195">
   <si>
     <t>UA名字</t>
   </si>
@@ -614,6 +614,9 @@
   </si>
   <si>
     <t>7840</t>
+  </si>
+  <si>
+    <t>6913</t>
   </si>
 </sst>
 </file>
@@ -1265,10 +1268,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1606,1551 +1609,1555 @@
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="3"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="3"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="3"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="3"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="3"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C19" s="3"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C20" s="3"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C21" s="3"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="3"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="3"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C24" s="3"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C25" s="3"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C26" s="3"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="3"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C30" s="3"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C31" s="3"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C32" s="3"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C33" s="3"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C34" s="3"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C35" s="3"/>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C36" s="3"/>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C37" s="3"/>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C38" s="3"/>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C39" s="3"/>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C40" s="3"/>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C41" s="3"/>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C42" s="3"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C43" s="3"/>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C44" s="3"/>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C45" s="3"/>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C46" s="3"/>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C47" s="3"/>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C48" s="3"/>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C49" s="3"/>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C50" s="3"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C51" s="3"/>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C52" s="3"/>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C53" s="3"/>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C54" s="3"/>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C55" s="3"/>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C56" s="3"/>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C57" s="3"/>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C58" s="3"/>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C59" s="3"/>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C60" s="3"/>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C61" s="3"/>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C62" s="3"/>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C63" s="3"/>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C64" s="3"/>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C65" s="3"/>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C66" s="3"/>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C67" s="3"/>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C68" s="3"/>
     </row>
     <row r="69" spans="1:3">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C69" s="3"/>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70" s="4" t="s">
+      <c r="A70" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C70" s="3"/>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="4" t="s">
+      <c r="A71" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C71" s="3"/>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C72" s="3"/>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="4" t="s">
+      <c r="A73" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C73" s="3"/>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C74" s="3"/>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="4" t="s">
+      <c r="A75" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C75" s="3"/>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C76" s="3"/>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="4" t="s">
+      <c r="A77" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B77" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C77" s="3"/>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" s="4" t="s">
+      <c r="A78" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B78" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C78" s="3"/>
     </row>
     <row r="79" spans="1:3">
-      <c r="A79" s="4" t="s">
+      <c r="A79" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="B79" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C79" s="3"/>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="4" t="s">
+      <c r="A80" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B80" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C80" s="3"/>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="4" t="s">
+      <c r="A81" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="B81" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C81" s="3"/>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="4" t="s">
+      <c r="A82" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B82" s="4" t="s">
+      <c r="B82" s="2" t="s">
         <v>90</v>
       </c>
       <c r="C82" s="3"/>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="4" t="s">
+      <c r="A83" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="B83" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C83" s="3"/>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="4" t="s">
+      <c r="A84" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B84" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C84" s="3"/>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="4" t="s">
+      <c r="A85" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C85" s="3"/>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="4" t="s">
+      <c r="A86" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C86" s="3"/>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="5" t="s">
+      <c r="A87" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="B87" s="4" t="s">
         <v>95</v>
       </c>
       <c r="C87" s="3"/>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="5" t="s">
+      <c r="A88" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B88" s="5" t="s">
+      <c r="B88" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C88" s="3"/>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="5" t="s">
+      <c r="A89" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B89" s="5" t="s">
+      <c r="B89" s="4" t="s">
         <v>97</v>
       </c>
       <c r="C89" s="3"/>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="4" t="s">
+      <c r="A90" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="B90" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C90" s="3"/>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="4" t="s">
+      <c r="A91" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C91" s="3"/>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="4" t="s">
+      <c r="A92" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B92" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C92" s="3"/>
     </row>
     <row r="93" spans="1:3">
-      <c r="A93" s="4" t="s">
+      <c r="A93" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B93" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C93" s="3"/>
     </row>
     <row r="94" spans="1:3">
-      <c r="A94" s="4" t="s">
+      <c r="A94" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B94" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C94" s="3"/>
     </row>
     <row r="95" spans="1:3">
-      <c r="A95" s="4" t="s">
+      <c r="A95" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B95" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C95" s="3"/>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="4" t="s">
+      <c r="A96" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B96" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C96" s="3"/>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="4" t="s">
+      <c r="A97" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B97" s="5" t="s">
+      <c r="B97" s="4" t="s">
         <v>107</v>
       </c>
       <c r="C97" s="3"/>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98" s="4" t="s">
+      <c r="A98" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B98" s="5" t="s">
+      <c r="B98" s="4" t="s">
         <v>109</v>
       </c>
       <c r="C98" s="3"/>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="4" t="s">
+      <c r="A99" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B99" s="5" t="s">
+      <c r="B99" s="4" t="s">
         <v>110</v>
       </c>
       <c r="C99" s="3"/>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="4" t="s">
+      <c r="A100" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B100" s="5" t="s">
+      <c r="B100" s="4" t="s">
         <v>111</v>
       </c>
       <c r="C100" s="3"/>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101" s="4" t="s">
+      <c r="A101" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B101" s="5" t="s">
+      <c r="B101" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C101" s="3"/>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102" s="4" t="s">
+      <c r="A102" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B102" s="5" t="s">
+      <c r="B102" s="4" t="s">
         <v>113</v>
       </c>
       <c r="C102" s="3"/>
     </row>
     <row r="103" spans="1:3">
-      <c r="A103" s="4" t="s">
+      <c r="A103" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B103" s="5" t="s">
+      <c r="B103" s="4" t="s">
         <v>114</v>
       </c>
       <c r="C103" s="3"/>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="4" t="s">
+      <c r="A104" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B104" s="5" t="s">
+      <c r="B104" s="4" t="s">
         <v>116</v>
       </c>
       <c r="C104" s="3"/>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="4" t="s">
+      <c r="A105" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B105" s="5" t="s">
+      <c r="B105" s="4" t="s">
         <v>117</v>
       </c>
       <c r="C105" s="3"/>
     </row>
     <row r="106" spans="1:3">
-      <c r="A106" s="4" t="s">
+      <c r="A106" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B106" s="5" t="s">
+      <c r="B106" s="4" t="s">
         <v>118</v>
       </c>
       <c r="C106" s="3"/>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107" s="4" t="s">
+      <c r="A107" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B107" s="5" t="s">
+      <c r="B107" s="4" t="s">
         <v>120</v>
       </c>
       <c r="C107" s="3"/>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="4" t="s">
+      <c r="A108" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B108" s="5" t="s">
+      <c r="B108" s="4" t="s">
         <v>122</v>
       </c>
       <c r="C108" s="3"/>
     </row>
     <row r="109" spans="1:3">
-      <c r="A109" s="4" t="s">
+      <c r="A109" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B109" s="5" t="s">
+      <c r="B109" s="4" t="s">
         <v>123</v>
       </c>
       <c r="C109" s="3"/>
     </row>
     <row r="110" spans="1:3">
-      <c r="A110" s="4" t="s">
+      <c r="A110" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B110" s="4" t="s">
+      <c r="B110" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C110" s="3"/>
     </row>
     <row r="111" spans="1:3">
-      <c r="A111" s="4" t="s">
+      <c r="A111" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B111" s="4" t="s">
+      <c r="B111" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C111" s="3"/>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="4" t="s">
+      <c r="A112" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B112" s="4" t="s">
+      <c r="B112" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C112" s="3"/>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="4" t="s">
+      <c r="A113" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B113" s="4" t="s">
+      <c r="B113" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C113" s="3"/>
     </row>
     <row r="114" spans="1:3">
-      <c r="A114" s="4" t="s">
+      <c r="A114" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B114" s="4" t="s">
+      <c r="B114" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C114" s="3"/>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="4" t="s">
+      <c r="A115" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B115" s="4" t="s">
+      <c r="B115" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C115" s="3"/>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="4" t="s">
+      <c r="A116" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B116" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C116" s="3"/>
     </row>
     <row r="117" spans="1:3">
-      <c r="A117" s="4" t="s">
+      <c r="A117" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="B117" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C117" s="3"/>
     </row>
     <row r="118" spans="1:3">
-      <c r="A118" s="4" t="s">
+      <c r="A118" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B118" s="4" t="s">
+      <c r="B118" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C118" s="3"/>
     </row>
     <row r="119" spans="1:3">
-      <c r="A119" s="4" t="s">
+      <c r="A119" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B119" s="4" t="s">
+      <c r="B119" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C119" s="3"/>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="4" t="s">
+      <c r="A120" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B120" s="4" t="s">
+      <c r="B120" s="2" t="s">
         <v>134</v>
       </c>
       <c r="C120" s="3"/>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="4" t="s">
+      <c r="A121" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B121" s="4" t="s">
+      <c r="B121" s="2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="122" spans="1:3">
-      <c r="A122" s="4" t="s">
+      <c r="A122" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B122" s="4" t="s">
+      <c r="B122" s="2" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="4" t="s">
+      <c r="A123" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B123" s="4" t="s">
+      <c r="B123" s="2" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="4" t="s">
+      <c r="A124" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B124" s="4" t="s">
+      <c r="B124" s="2" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="125" spans="1:3">
-      <c r="A125" s="4" t="s">
+      <c r="A125" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B125" s="4" t="s">
+      <c r="B125" s="2" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="126" spans="1:3">
-      <c r="A126" s="4" t="s">
+      <c r="A126" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B126" s="4" t="s">
+      <c r="B126" s="2" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="127" spans="1:3">
-      <c r="A127" s="4" t="s">
+      <c r="A127" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B127" s="4" t="s">
+      <c r="B127" s="2" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="4" t="s">
+      <c r="A128" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B128" s="4" t="s">
+      <c r="B128" s="2" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="4" t="s">
+      <c r="A129" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B129" s="4" t="s">
+      <c r="B129" s="2" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="130" spans="1:2">
-      <c r="A130" s="4" t="s">
+      <c r="A130" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B130" s="4" t="s">
+      <c r="B130" s="2" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="4" t="s">
+      <c r="A131" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B131" s="4" t="s">
+      <c r="B131" s="2" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="132" spans="1:2">
-      <c r="A132" s="4" t="s">
+      <c r="A132" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B132" s="4" t="s">
+      <c r="B132" s="2" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="4" t="s">
+      <c r="A133" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B133" s="4" t="s">
+      <c r="B133" s="2" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="4" t="s">
+      <c r="A134" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B134" s="4" t="s">
+      <c r="B134" s="2" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="4" t="s">
+      <c r="A135" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B135" s="4" t="s">
+      <c r="B135" s="2" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="4" t="s">
+      <c r="A136" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B136" s="4" t="s">
+      <c r="B136" s="2" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="4" t="s">
+      <c r="A137" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B137" s="4" t="s">
+      <c r="B137" s="2" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="4" t="s">
+      <c r="A138" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B138" s="4" t="s">
+      <c r="B138" s="2" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="4" t="s">
+      <c r="A139" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B139" s="4" t="s">
+      <c r="B139" s="2" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="4" t="s">
+      <c r="A140" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B140" s="4" t="s">
+      <c r="B140" s="2" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="4" t="s">
+      <c r="A141" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B141" s="4" t="s">
+      <c r="B141" s="2" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="4" t="s">
+      <c r="A142" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B142" s="4" t="s">
+      <c r="B142" s="2" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="4" t="s">
+      <c r="A143" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B143" s="4" t="s">
+      <c r="B143" s="2" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="4" t="s">
+      <c r="A144" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B144" s="4" t="s">
+      <c r="B144" s="2" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="4" t="s">
+      <c r="A145" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B145" s="4" t="s">
+      <c r="B145" s="2" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="4" t="s">
+      <c r="A146" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B146" s="4" t="s">
+      <c r="B146" s="2" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="4" t="s">
+      <c r="A147" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B147" s="4" t="s">
+      <c r="B147" s="2" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="4" t="s">
+      <c r="A148" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B148" s="4" t="s">
+      <c r="B148" s="2" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="4" t="s">
+      <c r="A149" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B149" s="4" t="s">
+      <c r="B149" s="2" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="4" t="s">
+      <c r="A150" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B150" s="4" t="s">
+      <c r="B150" s="2" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="4" t="s">
+      <c r="A151" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B151" s="4" t="s">
+      <c r="B151" s="2" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="4" t="s">
+      <c r="A152" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B152" s="4" t="s">
+      <c r="B152" s="2" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="4" t="s">
+      <c r="A153" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B153" s="4" t="s">
+      <c r="B153" s="2" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="4" t="s">
+      <c r="A154" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B154" s="4" t="s">
+      <c r="B154" s="2" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="4" t="s">
+      <c r="A155" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B155" s="4" t="s">
+      <c r="B155" s="2" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="4" t="s">
+      <c r="A156" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B156" s="4" t="s">
+      <c r="B156" s="2" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="4" t="s">
+      <c r="A157" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B157" s="4" t="s">
+      <c r="B157" s="2" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="4" t="s">
+      <c r="A158" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B158" s="4" t="s">
+      <c r="B158" s="2" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="4" t="s">
+      <c r="A159" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B159" s="4" t="s">
+      <c r="B159" s="2" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="4" t="s">
+      <c r="A160" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B160" s="4" t="s">
+      <c r="B160" s="2" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="4" t="s">
+      <c r="A161" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B161" s="4" t="s">
+      <c r="B161" s="2" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="4" t="s">
+      <c r="A162" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B162" s="4" t="s">
+      <c r="B162" s="2" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="4" t="s">
+      <c r="A163" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B163" s="4" t="s">
+      <c r="B163" s="2" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="4" t="s">
+      <c r="A164" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B164" s="4" t="s">
+      <c r="B164" s="2" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="4" t="s">
+      <c r="A165" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B165" s="4" t="s">
+      <c r="B165" s="2" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="4" t="s">
+      <c r="A166" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B166" s="4" t="s">
+      <c r="B166" s="2" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="4" t="s">
+      <c r="A167" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B167" s="4" t="s">
+      <c r="B167" s="2" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="4" t="s">
+      <c r="A168" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B168" s="4" t="s">
+      <c r="B168" s="2" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="4" t="s">
+      <c r="A169" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B169" s="4" t="s">
+      <c r="B169" s="2" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="4" t="s">
+      <c r="A170" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B170" s="4" t="s">
+      <c r="B170" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="4" t="s">
+      <c r="A171" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B171" s="4" t="s">
+      <c r="B171" s="2" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="4" t="s">
+      <c r="A172" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B172" s="4" t="s">
+      <c r="B172" s="2" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="4" t="s">
+      <c r="A173" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B173" s="4" t="s">
+      <c r="B173" s="2" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="4" t="s">
+      <c r="A174" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B174" s="4" t="s">
+      <c r="B174" s="2" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="4" t="s">
+      <c r="A175" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B175" s="4" t="s">
+      <c r="B175" s="2" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="4" t="s">
+      <c r="A176" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B176" s="4" t="s">
+      <c r="B176" s="2" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="4" t="s">
+      <c r="A177" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B177" s="4" t="s">
+      <c r="B177" s="2" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="4" t="s">
+      <c r="A178" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B178" s="4" t="s">
+      <c r="B178" s="2" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="4" t="s">
+      <c r="A179" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B179" s="4" t="s">
+      <c r="B179" s="2" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="2"/>
-      <c r="B180" s="2"/>
+      <c r="A180" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>194</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="198">
   <si>
     <t>UA名字</t>
   </si>
@@ -617,6 +617,15 @@
   </si>
   <si>
     <t>6913</t>
+  </si>
+  <si>
+    <t>4355</t>
+  </si>
+  <si>
+    <t>3695</t>
+  </si>
+  <si>
+    <t>4343</t>
   </si>
 </sst>
 </file>
@@ -1593,7 +1602,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C180"/>
+  <dimension ref="A1:C183"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3152,11 +3161,35 @@
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="5" t="s">
+      <c r="A180" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B180" s="5" t="s">
+      <c r="B180" s="2" t="s">
         <v>194</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -1268,7 +1268,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1278,9 +1278,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3169,26 +3166,26 @@
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="5" t="s">
+      <c r="A181" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B181" s="5" t="s">
+      <c r="B181" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B182" s="5" t="s">
+      <c r="A182" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B182" s="2" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="5" t="s">
+      <c r="A183" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B183" s="5" t="s">
+      <c r="B183" s="2" t="s">
         <v>197</v>
       </c>
     </row>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="199">
   <si>
     <t>UA名字</t>
   </si>
@@ -626,6 +626,9 @@
   </si>
   <si>
     <t>4343</t>
+  </si>
+  <si>
+    <t>1552</t>
   </si>
 </sst>
 </file>
@@ -1268,7 +1271,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1278,6 +1281,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1599,7 +1605,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C183"/>
+  <dimension ref="A1:C184"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3150,43 +3156,51 @@
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B179" s="2" t="s">
+      <c r="A179" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B179" s="5" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="2" t="s">
+      <c r="A180" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B180" s="2" t="s">
+      <c r="B180" s="5" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="2" t="s">
+      <c r="A181" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B181" s="2" t="s">
+      <c r="B181" s="5" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="2" t="s">
+      <c r="A182" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B182" s="2" t="s">
+      <c r="B182" s="5" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="2" t="s">
+      <c r="A183" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B183" s="2" t="s">
+      <c r="B183" s="5" t="s">
         <v>197</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="200">
   <si>
     <t>UA名字</t>
   </si>
@@ -629,6 +629,9 @@
   </si>
   <si>
     <t>1552</t>
+  </si>
+  <si>
+    <t>0603</t>
   </si>
 </sst>
 </file>
@@ -1605,7 +1608,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C184"/>
+  <dimension ref="A1:C185"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3156,51 +3159,59 @@
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="5" t="s">
+      <c r="A179" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B179" s="5" t="s">
+      <c r="B179" s="2" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="5" t="s">
+      <c r="A180" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B180" s="5" t="s">
+      <c r="B180" s="2" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="5" t="s">
+      <c r="A181" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B181" s="5" t="s">
+      <c r="B181" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="5" t="s">
+      <c r="A182" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B182" s="5" t="s">
+      <c r="B182" s="2" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="5" t="s">
+      <c r="A183" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B183" s="5" t="s">
+      <c r="B183" s="2" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="5" t="s">
+      <c r="A184" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B184" s="5" t="s">
+      <c r="B184" s="2" t="s">
         <v>198</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>199</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="201">
   <si>
     <t>UA名字</t>
   </si>
@@ -632,6 +632,9 @@
   </si>
   <si>
     <t>0603</t>
+  </si>
+  <si>
+    <t>3335</t>
   </si>
 </sst>
 </file>
@@ -1608,7 +1611,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C185"/>
+  <dimension ref="A1:C186"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3207,11 +3210,19 @@
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="5" t="s">
+      <c r="A185" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B185" s="5" t="s">
+      <c r="B185" s="2" t="s">
         <v>199</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="202">
   <si>
     <t>UA名字</t>
   </si>
@@ -635,6 +635,9 @@
   </si>
   <si>
     <t>3335</t>
+  </si>
+  <si>
+    <t>7976</t>
   </si>
 </sst>
 </file>
@@ -1611,7 +1614,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C186"/>
+  <dimension ref="A1:C187"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3218,11 +3221,19 @@
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="5" t="s">
+      <c r="A186" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B186" s="5" t="s">
+      <c r="B186" s="2" t="s">
         <v>200</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>201</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="203">
   <si>
     <t>UA名字</t>
   </si>
@@ -638,6 +638,9 @@
   </si>
   <si>
     <t>7976</t>
+  </si>
+  <si>
+    <t>6733</t>
   </si>
 </sst>
 </file>
@@ -1614,7 +1617,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C187"/>
+  <dimension ref="A1:C188"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3229,11 +3232,19 @@
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="5" t="s">
+      <c r="A187" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B187" s="5" t="s">
+      <c r="B187" s="2" t="s">
         <v>201</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="204">
   <si>
     <t>UA名字</t>
   </si>
@@ -641,6 +641,9 @@
   </si>
   <si>
     <t>6733</t>
+  </si>
+  <si>
+    <t>2090</t>
   </si>
 </sst>
 </file>
@@ -1283,7 +1286,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1293,9 +1296,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1617,7 +1617,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C188"/>
+  <dimension ref="A1:C189"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3240,11 +3240,19 @@
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="5" t="s">
+      <c r="A188" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B188" s="5" t="s">
+      <c r="B188" s="2" t="s">
         <v>202</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="205">
   <si>
     <t>UA名字</t>
   </si>
@@ -644,6 +644,9 @@
   </si>
   <si>
     <t>2090</t>
+  </si>
+  <si>
+    <t>6137</t>
   </si>
 </sst>
 </file>
@@ -1617,7 +1620,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C189"/>
+  <dimension ref="A1:C190"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3255,6 +3258,14 @@
         <v>203</v>
       </c>
     </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>204</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="207">
   <si>
     <t>UA名字</t>
   </si>
@@ -647,6 +647,12 @@
   </si>
   <si>
     <t>6137</t>
+  </si>
+  <si>
+    <t>0913</t>
+  </si>
+  <si>
+    <t>5016</t>
   </si>
 </sst>
 </file>
@@ -1289,7 +1295,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1299,6 +1305,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1620,7 +1629,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C190"/>
+  <dimension ref="A1:C192"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3266,6 +3275,22 @@
         <v>204</v>
       </c>
     </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="209">
   <si>
     <t>UA名字</t>
   </si>
@@ -653,6 +653,12 @@
   </si>
   <si>
     <t>5016</t>
+  </si>
+  <si>
+    <t>0083</t>
+  </si>
+  <si>
+    <t>7885</t>
   </si>
 </sst>
 </file>
@@ -1629,7 +1635,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C192"/>
+  <dimension ref="A1:C194"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3276,19 +3282,35 @@
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="5" t="s">
+      <c r="A191" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B191" s="5" t="s">
+      <c r="B191" s="2" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="5" t="s">
+      <c r="A192" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B192" s="5" t="s">
+      <c r="B192" s="2" t="s">
         <v>206</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="211">
   <si>
     <t>UA名字</t>
   </si>
@@ -659,6 +659,12 @@
   </si>
   <si>
     <t>7885</t>
+  </si>
+  <si>
+    <t>3510</t>
+  </si>
+  <si>
+    <t>1400</t>
   </si>
 </sst>
 </file>
@@ -1635,7 +1641,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C194"/>
+  <dimension ref="A1:C196"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3298,19 +3304,35 @@
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="5" t="s">
+      <c r="A193" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B193" s="5" t="s">
+      <c r="B193" s="2" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="5" t="s">
+      <c r="A194" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B194" s="5" t="s">
+      <c r="B194" s="2" t="s">
         <v>208</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="217">
   <si>
     <t>UA名字</t>
   </si>
@@ -665,6 +665,24 @@
   </si>
   <si>
     <t>1400</t>
+  </si>
+  <si>
+    <t>0344</t>
+  </si>
+  <si>
+    <t>7478</t>
+  </si>
+  <si>
+    <t>7239</t>
+  </si>
+  <si>
+    <t>5578</t>
+  </si>
+  <si>
+    <t>2117</t>
+  </si>
+  <si>
+    <t>3686</t>
   </si>
 </sst>
 </file>
@@ -1641,7 +1659,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C196"/>
+  <dimension ref="A1:C202"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3320,19 +3338,67 @@
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="5" t="s">
+      <c r="A195" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B195" s="5" t="s">
+      <c r="B195" s="2" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="5" t="s">
+      <c r="A196" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B196" s="5" t="s">
+      <c r="B196" s="2" t="s">
         <v>210</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="222">
   <si>
     <t>UA名字</t>
   </si>
@@ -683,6 +683,21 @@
   </si>
   <si>
     <t>3686</t>
+  </si>
+  <si>
+    <t>4606</t>
+  </si>
+  <si>
+    <t>2674</t>
+  </si>
+  <si>
+    <t>6233</t>
+  </si>
+  <si>
+    <t>4132</t>
+  </si>
+  <si>
+    <t>8242</t>
   </si>
 </sst>
 </file>
@@ -1659,7 +1674,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C202"/>
+  <dimension ref="A1:C207"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3354,51 +3369,91 @@
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="5" t="s">
+      <c r="A197" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B197" s="5" t="s">
+      <c r="B197" s="2" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="5" t="s">
+      <c r="A198" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B198" s="5" t="s">
+      <c r="B198" s="2" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="5" t="s">
+      <c r="A199" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B199" s="5" t="s">
+      <c r="B199" s="2" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="5" t="s">
+      <c r="A200" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B200" s="5" t="s">
+      <c r="B200" s="2" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="5" t="s">
+      <c r="A201" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B201" s="5" t="s">
+      <c r="B201" s="2" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="5" t="s">
+      <c r="A202" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B202" s="5" t="s">
+      <c r="B202" s="2" t="s">
         <v>216</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="224">
   <si>
     <t>UA名字</t>
   </si>
@@ -698,6 +698,12 @@
   </si>
   <si>
     <t>8242</t>
+  </si>
+  <si>
+    <t>1873</t>
+  </si>
+  <si>
+    <t>4941</t>
   </si>
 </sst>
 </file>
@@ -1674,7 +1680,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C207"/>
+  <dimension ref="A1:C209"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3417,43 +3423,59 @@
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="5" t="s">
+      <c r="A203" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B203" s="5" t="s">
+      <c r="B203" s="2" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="5" t="s">
+      <c r="A204" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B204" s="5" t="s">
+      <c r="B204" s="2" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="5" t="s">
+      <c r="A205" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B205" s="5" t="s">
+      <c r="B205" s="2" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="5" t="s">
+      <c r="A206" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B206" s="5" t="s">
+      <c r="B206" s="2" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="5" t="s">
+      <c r="A207" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B207" s="5" t="s">
+      <c r="B207" s="2" t="s">
         <v>221</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>223</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="225">
   <si>
     <t>UA名字</t>
   </si>
@@ -704,6 +704,9 @@
   </si>
   <si>
     <t>4941</t>
+  </si>
+  <si>
+    <t>8373</t>
   </si>
 </sst>
 </file>
@@ -1680,7 +1683,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C209"/>
+  <dimension ref="A1:C210"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3463,19 +3466,27 @@
       </c>
     </row>
     <row r="208" spans="1:2">
-      <c r="A208" s="5" t="s">
+      <c r="A208" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B208" s="5" t="s">
+      <c r="B208" s="2" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="5" t="s">
+      <c r="A209" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B209" s="5" t="s">
+      <c r="B209" s="2" t="s">
         <v>223</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>224</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="226">
   <si>
     <t>UA名字</t>
   </si>
@@ -707,6 +707,9 @@
   </si>
   <si>
     <t>8373</t>
+  </si>
+  <si>
+    <t>8857</t>
   </si>
 </sst>
 </file>
@@ -1683,7 +1686,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C210"/>
+  <dimension ref="A1:C211"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3482,11 +3485,19 @@
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="5" t="s">
+      <c r="A210" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B210" s="5" t="s">
+      <c r="B210" s="2" t="s">
         <v>224</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>225</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="227">
   <si>
     <t>UA名字</t>
   </si>
@@ -710,6 +710,9 @@
   </si>
   <si>
     <t>8857</t>
+  </si>
+  <si>
+    <t>3472</t>
   </si>
 </sst>
 </file>
@@ -1686,7 +1689,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C211"/>
+  <dimension ref="A1:C212"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3493,11 +3496,19 @@
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="5" t="s">
+      <c r="A211" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B211" s="5" t="s">
+      <c r="B211" s="2" t="s">
         <v>225</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -3505,10 +3505,10 @@
     </row>
     <row r="212" spans="1:2">
       <c r="A212" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B212" s="5" t="s">
         <v>226</v>
-      </c>
-      <c r="B212" s="5" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="228">
   <si>
     <t>UA名字</t>
   </si>
@@ -713,6 +713,9 @@
   </si>
   <si>
     <t>3472</t>
+  </si>
+  <si>
+    <t>6324</t>
   </si>
 </sst>
 </file>
@@ -1689,7 +1692,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C212"/>
+  <dimension ref="A1:C213"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3504,11 +3507,19 @@
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="5" t="s">
+      <c r="A212" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B212" s="5" t="s">
+      <c r="B212" s="2" t="s">
         <v>226</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -712,7 +712,7 @@
     <t>8857</t>
   </si>
   <si>
-    <t>3472</t>
+    <t>9008</t>
   </si>
   <si>
     <t>6324</t>
@@ -1358,7 +1358,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1368,9 +1368,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3507,18 +3504,18 @@
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="2" t="s">
+      <c r="A212" t="s">
         <v>39</v>
       </c>
-      <c r="B212" s="2" t="s">
+      <c r="B212" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="5" t="s">
+      <c r="A213" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B213" s="5" t="s">
+      <c r="B213" s="2" t="s">
         <v>227</v>
       </c>
     </row>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="229">
   <si>
     <t>UA名字</t>
   </si>
@@ -716,6 +716,9 @@
   </si>
   <si>
     <t>6324</t>
+  </si>
+  <si>
+    <t>7331</t>
   </si>
 </sst>
 </file>
@@ -1358,7 +1361,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1368,6 +1371,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1689,7 +1695,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C213"/>
+  <dimension ref="A1:C214"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3519,6 +3525,14 @@
         <v>227</v>
       </c>
     </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>228</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="235">
   <si>
     <t>UA名字</t>
   </si>
@@ -719,6 +719,24 @@
   </si>
   <si>
     <t>7331</t>
+  </si>
+  <si>
+    <t>8460</t>
+  </si>
+  <si>
+    <t>8426</t>
+  </si>
+  <si>
+    <t>1884</t>
+  </si>
+  <si>
+    <t>6009</t>
+  </si>
+  <si>
+    <t>6072</t>
+  </si>
+  <si>
+    <t>7801</t>
   </si>
 </sst>
 </file>
@@ -1695,7 +1713,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C214"/>
+  <dimension ref="A1:C220"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3526,11 +3544,59 @@
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="5" t="s">
+      <c r="A214" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B214" s="5" t="s">
+      <c r="B214" s="2" t="s">
         <v>228</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="236">
   <si>
     <t>UA名字</t>
   </si>
@@ -737,6 +737,9 @@
   </si>
   <si>
     <t>7801</t>
+  </si>
+  <si>
+    <t>3137</t>
   </si>
 </sst>
 </file>
@@ -1713,7 +1716,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C220"/>
+  <dimension ref="A1:C221"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3552,51 +3555,59 @@
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="5" t="s">
+      <c r="A215" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B215" s="5" t="s">
+      <c r="B215" s="2" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="5" t="s">
+      <c r="A216" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B216" s="5" t="s">
+      <c r="B216" s="2" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="5" t="s">
+      <c r="A217" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B217" s="5" t="s">
+      <c r="B217" s="2" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="5" t="s">
+      <c r="A218" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B218" s="5" t="s">
+      <c r="B218" s="2" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="5" t="s">
+      <c r="A219" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B219" s="5" t="s">
+      <c r="B219" s="2" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="220" spans="1:2">
-      <c r="A220" s="5" t="s">
+      <c r="A220" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B220" s="5" t="s">
+      <c r="B220" s="2" t="s">
         <v>234</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="235">
   <si>
     <t>UA名字</t>
   </si>
@@ -641,9 +641,6 @@
   </si>
   <si>
     <t>6733</t>
-  </si>
-  <si>
-    <t>2090</t>
   </si>
   <si>
     <t>6137</t>
@@ -1391,10 +1388,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1732,1882 +1729,1882 @@
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="3"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="3"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="3"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="3"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="3"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C19" s="3"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C20" s="3"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C21" s="3"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="3"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="3"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C24" s="3"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C25" s="3"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C26" s="3"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="3"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="4" t="s">
         <v>32</v>
       </c>
       <c r="C30" s="3"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C31" s="3"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C32" s="3"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C33" s="3"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C34" s="3"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C35" s="3"/>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C36" s="3"/>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C37" s="3"/>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C38" s="3"/>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C39" s="3"/>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C40" s="3"/>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="4" t="s">
         <v>44</v>
       </c>
       <c r="C41" s="3"/>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C42" s="3"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C43" s="3"/>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="4" t="s">
         <v>48</v>
       </c>
       <c r="C44" s="3"/>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="4" t="s">
         <v>49</v>
       </c>
       <c r="C45" s="3"/>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C46" s="3"/>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C47" s="3"/>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C48" s="3"/>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="4" t="s">
         <v>53</v>
       </c>
       <c r="C49" s="3"/>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="4" t="s">
         <v>54</v>
       </c>
       <c r="C50" s="3"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="4" t="s">
         <v>55</v>
       </c>
       <c r="C51" s="3"/>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="4" t="s">
         <v>57</v>
       </c>
       <c r="C52" s="3"/>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="4" t="s">
         <v>58</v>
       </c>
       <c r="C53" s="3"/>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="4" t="s">
         <v>59</v>
       </c>
       <c r="C54" s="3"/>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="4" t="s">
         <v>60</v>
       </c>
       <c r="C55" s="3"/>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="4" t="s">
         <v>61</v>
       </c>
       <c r="C56" s="3"/>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="4" t="s">
         <v>62</v>
       </c>
       <c r="C57" s="3"/>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="4" t="s">
         <v>63</v>
       </c>
       <c r="C58" s="3"/>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="4" t="s">
         <v>64</v>
       </c>
       <c r="C59" s="3"/>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="4" t="s">
         <v>65</v>
       </c>
       <c r="C60" s="3"/>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="2" t="s">
+      <c r="A61" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="4" t="s">
         <v>66</v>
       </c>
       <c r="C61" s="3"/>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="2" t="s">
+      <c r="A62" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="4" t="s">
         <v>67</v>
       </c>
       <c r="C62" s="3"/>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C63" s="3"/>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="2" t="s">
+      <c r="A64" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="4" t="s">
         <v>70</v>
       </c>
       <c r="C64" s="3"/>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C65" s="3"/>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66" s="2" t="s">
+      <c r="A66" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="4" t="s">
         <v>72</v>
       </c>
       <c r="C66" s="3"/>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="2" t="s">
+      <c r="A67" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C67" s="3"/>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="2" t="s">
+      <c r="A68" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="4" t="s">
         <v>74</v>
       </c>
       <c r="C68" s="3"/>
     </row>
     <row r="69" spans="1:3">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="4" t="s">
         <v>75</v>
       </c>
       <c r="C69" s="3"/>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70" s="2" t="s">
+      <c r="A70" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="4" t="s">
         <v>76</v>
       </c>
       <c r="C70" s="3"/>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="2" t="s">
+      <c r="A71" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="4" t="s">
         <v>77</v>
       </c>
       <c r="C71" s="3"/>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="2" t="s">
+      <c r="A72" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C72" s="3"/>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="2" t="s">
+      <c r="A73" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="4" t="s">
         <v>80</v>
       </c>
       <c r="C73" s="3"/>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74" s="2" t="s">
+      <c r="A74" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="4" t="s">
         <v>81</v>
       </c>
       <c r="C74" s="3"/>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="2" t="s">
+      <c r="A75" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="4" t="s">
         <v>82</v>
       </c>
       <c r="C75" s="3"/>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="2" t="s">
+      <c r="A76" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" s="4" t="s">
         <v>83</v>
       </c>
       <c r="C76" s="3"/>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C77" s="3"/>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" s="2" t="s">
+      <c r="A78" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C78" s="3"/>
     </row>
     <row r="79" spans="1:3">
-      <c r="A79" s="2" t="s">
+      <c r="A79" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B79" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C79" s="3"/>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="2" t="s">
+      <c r="A80" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" s="4" t="s">
         <v>88</v>
       </c>
       <c r="C80" s="3"/>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="2" t="s">
+      <c r="A81" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B81" s="4" t="s">
         <v>89</v>
       </c>
       <c r="C81" s="3"/>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="2" t="s">
+      <c r="A82" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B82" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C82" s="3"/>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="2" t="s">
+      <c r="A83" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B83" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C83" s="3"/>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="2" t="s">
+      <c r="A84" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B84" s="4" t="s">
         <v>92</v>
       </c>
       <c r="C84" s="3"/>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="2" t="s">
+      <c r="A85" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B85" s="4" t="s">
         <v>93</v>
       </c>
       <c r="C85" s="3"/>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="2" t="s">
+      <c r="A86" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="B86" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C86" s="3"/>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="4" t="s">
+      <c r="A87" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="B87" s="5" t="s">
         <v>95</v>
       </c>
       <c r="C87" s="3"/>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="4" t="s">
+      <c r="A88" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B88" s="4" t="s">
+      <c r="B88" s="5" t="s">
         <v>96</v>
       </c>
       <c r="C88" s="3"/>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="4" t="s">
+      <c r="A89" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B89" s="5" t="s">
         <v>97</v>
       </c>
       <c r="C89" s="3"/>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="2" t="s">
+      <c r="A90" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B90" s="4" t="s">
         <v>99</v>
       </c>
       <c r="C90" s="3"/>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="2" t="s">
+      <c r="A91" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B91" s="4" t="s">
         <v>100</v>
       </c>
       <c r="C91" s="3"/>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="2" t="s">
+      <c r="A92" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B92" s="4" t="s">
         <v>101</v>
       </c>
       <c r="C92" s="3"/>
     </row>
     <row r="93" spans="1:3">
-      <c r="A93" s="2" t="s">
+      <c r="A93" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B93" s="4" t="s">
         <v>102</v>
       </c>
       <c r="C93" s="3"/>
     </row>
     <row r="94" spans="1:3">
-      <c r="A94" s="2" t="s">
+      <c r="A94" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="B94" s="4" t="s">
         <v>103</v>
       </c>
       <c r="C94" s="3"/>
     </row>
     <row r="95" spans="1:3">
-      <c r="A95" s="2" t="s">
+      <c r="A95" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="B95" s="4" t="s">
         <v>105</v>
       </c>
       <c r="C95" s="3"/>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="2" t="s">
+      <c r="A96" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="B96" s="4" t="s">
         <v>106</v>
       </c>
       <c r="C96" s="3"/>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="2" t="s">
+      <c r="A97" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B97" s="5" t="s">
         <v>107</v>
       </c>
       <c r="C97" s="3"/>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98" s="2" t="s">
+      <c r="A98" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B98" s="5" t="s">
         <v>109</v>
       </c>
       <c r="C98" s="3"/>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="2" t="s">
+      <c r="A99" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B99" s="5" t="s">
         <v>110</v>
       </c>
       <c r="C99" s="3"/>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="2" t="s">
+      <c r="A100" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B100" s="5" t="s">
         <v>111</v>
       </c>
       <c r="C100" s="3"/>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101" s="2" t="s">
+      <c r="A101" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B101" s="4" t="s">
+      <c r="B101" s="5" t="s">
         <v>112</v>
       </c>
       <c r="C101" s="3"/>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102" s="2" t="s">
+      <c r="A102" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B102" s="5" t="s">
         <v>113</v>
       </c>
       <c r="C102" s="3"/>
     </row>
     <row r="103" spans="1:3">
-      <c r="A103" s="2" t="s">
+      <c r="A103" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="B103" s="5" t="s">
         <v>114</v>
       </c>
       <c r="C103" s="3"/>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="2" t="s">
+      <c r="A104" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="B104" s="5" t="s">
         <v>116</v>
       </c>
       <c r="C104" s="3"/>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="2" t="s">
+      <c r="A105" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="B105" s="5" t="s">
         <v>117</v>
       </c>
       <c r="C105" s="3"/>
     </row>
     <row r="106" spans="1:3">
-      <c r="A106" s="2" t="s">
+      <c r="A106" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="B106" s="5" t="s">
         <v>118</v>
       </c>
       <c r="C106" s="3"/>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107" s="2" t="s">
+      <c r="A107" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="B107" s="5" t="s">
         <v>120</v>
       </c>
       <c r="C107" s="3"/>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="2" t="s">
+      <c r="A108" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B108" s="4" t="s">
+      <c r="B108" s="5" t="s">
         <v>122</v>
       </c>
       <c r="C108" s="3"/>
     </row>
     <row r="109" spans="1:3">
-      <c r="A109" s="2" t="s">
+      <c r="A109" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B109" s="4" t="s">
+      <c r="B109" s="5" t="s">
         <v>123</v>
       </c>
       <c r="C109" s="3"/>
     </row>
     <row r="110" spans="1:3">
-      <c r="A110" s="2" t="s">
+      <c r="A110" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="B110" s="4" t="s">
         <v>124</v>
       </c>
       <c r="C110" s="3"/>
     </row>
     <row r="111" spans="1:3">
-      <c r="A111" s="2" t="s">
+      <c r="A111" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="B111" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C111" s="3"/>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="2" t="s">
+      <c r="A112" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="B112" s="4" t="s">
         <v>127</v>
       </c>
       <c r="C112" s="3"/>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="2" t="s">
+      <c r="A113" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="B113" s="4" t="s">
         <v>129</v>
       </c>
       <c r="C113" s="3"/>
     </row>
     <row r="114" spans="1:3">
-      <c r="A114" s="2" t="s">
+      <c r="A114" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="B114" s="4" t="s">
         <v>130</v>
       </c>
       <c r="C114" s="3"/>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="2" t="s">
+      <c r="A115" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="B115" s="4" t="s">
         <v>113</v>
       </c>
       <c r="C115" s="3"/>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="2" t="s">
+      <c r="A116" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="B116" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C116" s="3"/>
     </row>
     <row r="117" spans="1:3">
-      <c r="A117" s="2" t="s">
+      <c r="A117" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="B117" s="4" t="s">
         <v>131</v>
       </c>
       <c r="C117" s="3"/>
     </row>
     <row r="118" spans="1:3">
-      <c r="A118" s="2" t="s">
+      <c r="A118" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="B118" s="4" t="s">
         <v>132</v>
       </c>
       <c r="C118" s="3"/>
     </row>
     <row r="119" spans="1:3">
-      <c r="A119" s="2" t="s">
+      <c r="A119" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="B119" s="4" t="s">
         <v>133</v>
       </c>
       <c r="C119" s="3"/>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="2" t="s">
+      <c r="A120" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="B120" s="4" t="s">
         <v>134</v>
       </c>
       <c r="C120" s="3"/>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="2" t="s">
+      <c r="A121" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="B121" s="4" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="122" spans="1:3">
-      <c r="A122" s="2" t="s">
+      <c r="A122" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="B122" s="4" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="2" t="s">
+      <c r="A123" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="B123" s="4" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="2" t="s">
+      <c r="A124" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="B124" s="4" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="125" spans="1:3">
-      <c r="A125" s="2" t="s">
+      <c r="A125" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="B125" s="4" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="126" spans="1:3">
-      <c r="A126" s="2" t="s">
+      <c r="A126" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="B126" s="4" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="127" spans="1:3">
-      <c r="A127" s="2" t="s">
+      <c r="A127" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="B127" s="4" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="2" t="s">
+      <c r="A128" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="B128" s="4" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="2" t="s">
+      <c r="A129" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="B129" s="4" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="130" spans="1:2">
-      <c r="A130" s="2" t="s">
+      <c r="A130" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="B130" s="4" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="2" t="s">
+      <c r="A131" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="B131" s="4" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="132" spans="1:2">
-      <c r="A132" s="2" t="s">
+      <c r="A132" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="B132" s="4" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="2" t="s">
+      <c r="A133" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="B133" s="4" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="2" t="s">
+      <c r="A134" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="B134" s="4" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="2" t="s">
+      <c r="A135" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="B135" s="4" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="2" t="s">
+      <c r="A136" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="B136" s="4" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="2" t="s">
+      <c r="A137" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="B137" s="4" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="2" t="s">
+      <c r="A138" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="B138" s="4" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="2" t="s">
+      <c r="A139" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="B139" s="4" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="2" t="s">
+      <c r="A140" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="B140" s="4" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="2" t="s">
+      <c r="A141" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="B141" s="4" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="2" t="s">
+      <c r="A142" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B142" s="2" t="s">
+      <c r="B142" s="4" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="2" t="s">
+      <c r="A143" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B143" s="2" t="s">
+      <c r="B143" s="4" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="2" t="s">
+      <c r="A144" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B144" s="2" t="s">
+      <c r="B144" s="4" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="2" t="s">
+      <c r="A145" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B145" s="2" t="s">
+      <c r="B145" s="4" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="2" t="s">
+      <c r="A146" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B146" s="2" t="s">
+      <c r="B146" s="4" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="2" t="s">
+      <c r="A147" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B147" s="2" t="s">
+      <c r="B147" s="4" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="2" t="s">
+      <c r="A148" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B148" s="2" t="s">
+      <c r="B148" s="4" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="2" t="s">
+      <c r="A149" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B149" s="2" t="s">
+      <c r="B149" s="4" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="2" t="s">
+      <c r="A150" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B150" s="2" t="s">
+      <c r="B150" s="4" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="2" t="s">
+      <c r="A151" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="B151" s="4" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="2" t="s">
+      <c r="A152" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B152" s="2" t="s">
+      <c r="B152" s="4" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="2" t="s">
+      <c r="A153" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B153" s="2" t="s">
+      <c r="B153" s="4" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="2" t="s">
+      <c r="A154" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="B154" s="4" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="2" t="s">
+      <c r="A155" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B155" s="2" t="s">
+      <c r="B155" s="4" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="2" t="s">
+      <c r="A156" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B156" s="2" t="s">
+      <c r="B156" s="4" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="2" t="s">
+      <c r="A157" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B157" s="2" t="s">
+      <c r="B157" s="4" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="2" t="s">
+      <c r="A158" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B158" s="2" t="s">
+      <c r="B158" s="4" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="2" t="s">
+      <c r="A159" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B159" s="2" t="s">
+      <c r="B159" s="4" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="2" t="s">
+      <c r="A160" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B160" s="2" t="s">
+      <c r="B160" s="4" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="2" t="s">
+      <c r="A161" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B161" s="2" t="s">
+      <c r="B161" s="4" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="2" t="s">
+      <c r="A162" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B162" s="2" t="s">
+      <c r="B162" s="4" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="2" t="s">
+      <c r="A163" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="B163" s="4" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="2" t="s">
+      <c r="A164" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="B164" s="2" t="s">
+      <c r="B164" s="4" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="2" t="s">
+      <c r="A165" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B165" s="2" t="s">
+      <c r="B165" s="4" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="2" t="s">
+      <c r="A166" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B166" s="2" t="s">
+      <c r="B166" s="4" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="2" t="s">
+      <c r="A167" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B167" s="2" t="s">
+      <c r="B167" s="4" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="2" t="s">
+      <c r="A168" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B168" s="2" t="s">
+      <c r="B168" s="4" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="2" t="s">
+      <c r="A169" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B169" s="2" t="s">
+      <c r="B169" s="4" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="2" t="s">
+      <c r="A170" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B170" s="2" t="s">
+      <c r="B170" s="4" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="2" t="s">
+      <c r="A171" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B171" s="2" t="s">
+      <c r="B171" s="4" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="2" t="s">
+      <c r="A172" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B172" s="2" t="s">
+      <c r="B172" s="4" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="2" t="s">
+      <c r="A173" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B173" s="2" t="s">
+      <c r="B173" s="4" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="2" t="s">
+      <c r="A174" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B174" s="2" t="s">
+      <c r="B174" s="4" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="2" t="s">
+      <c r="A175" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B175" s="2" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2">
-      <c r="A176" s="2" t="s">
+      <c r="B178" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B182" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B176" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2">
-      <c r="A177" s="2" t="s">
+      <c r="B190" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B177" s="2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2">
-      <c r="A178" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2">
-      <c r="A179" s="2" t="s">
+      <c r="B194" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B179" s="2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2">
-      <c r="A180" s="2" t="s">
+      <c r="B199" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B180" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2">
-      <c r="A181" s="2" t="s">
+      <c r="B200" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B181" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2">
-      <c r="A182" s="2" t="s">
+      <c r="B203" s="4" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B182" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2">
-      <c r="A183" s="2" t="s">
+      <c r="B208" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B212" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B213" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B183" s="2" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2">
-      <c r="A184" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B184" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2">
-      <c r="A185" s="2" t="s">
+      <c r="B216" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B185" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2">
-      <c r="A186" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B186" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2">
-      <c r="A187" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B187" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2">
-      <c r="A188" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B188" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2">
-      <c r="A189" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B189" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2">
-      <c r="A190" s="1" t="s">
+      <c r="B217" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B190" s="1" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2">
-      <c r="A191" s="2" t="s">
+      <c r="B218" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B191" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2">
-      <c r="A192" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B192" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2">
-      <c r="A193" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B193" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2">
-      <c r="A194" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B194" s="2" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2">
-      <c r="A195" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B195" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2">
-      <c r="A196" s="2" t="s">
+      <c r="B219" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B196" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2">
-      <c r="A197" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B197" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2">
-      <c r="A198" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B198" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2">
-      <c r="A199" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B199" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2">
-      <c r="A200" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B200" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2">
-      <c r="A201" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2">
-      <c r="A202" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B202" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2">
-      <c r="A203" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2">
-      <c r="A204" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2">
-      <c r="A205" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2">
-      <c r="A206" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2">
-      <c r="A207" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2">
-      <c r="A208" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2">
-      <c r="A209" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2">
-      <c r="A210" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2">
-      <c r="A211" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2">
-      <c r="A212" t="s">
-        <v>39</v>
-      </c>
-      <c r="B212" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2">
-      <c r="A213" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B213" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2">
-      <c r="A214" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2">
-      <c r="A215" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2">
-      <c r="A216" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2">
-      <c r="A217" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B217" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2">
-      <c r="A218" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B218" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2">
-      <c r="A219" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B219" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2">
-      <c r="A220" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B220" s="2" t="s">
+      <c r="B220" s="4" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="5" t="s">
+      <c r="A221" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B221" s="5" t="s">
-        <v>235</v>
+      <c r="B221" s="2" t="s">
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="241">
   <si>
     <t>UA名字</t>
   </si>
@@ -737,6 +737,24 @@
   </si>
   <si>
     <t>3137</t>
+  </si>
+  <si>
+    <t>4097</t>
+  </si>
+  <si>
+    <t>4316</t>
+  </si>
+  <si>
+    <t>7174</t>
+  </si>
+  <si>
+    <t>7301</t>
+  </si>
+  <si>
+    <t>1788</t>
+  </si>
+  <si>
+    <t>7006</t>
   </si>
 </sst>
 </file>
@@ -1388,10 +1406,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1713,7 +1731,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C221"/>
+  <dimension ref="A1:C226"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -1729,1882 +1747,1922 @@
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="A5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="A7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="A8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="A9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="A10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="A11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12" s="4" t="s">
+      <c r="A12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="3"/>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B13" s="4" t="s">
+      <c r="A13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C13" s="3"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="A14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="3"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="5" t="s">
+      <c r="A15" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="3"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B16" s="5" t="s">
+      <c r="A16" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="3"/>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B17" s="5" t="s">
+      <c r="A17" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C17" s="3"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B18" s="5" t="s">
+      <c r="A18" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="3"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B19" s="5" t="s">
+      <c r="A19" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C19" s="3"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B20" s="5" t="s">
+      <c r="A20" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C20" s="3"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B21" s="5" t="s">
+      <c r="A21" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C21" s="3"/>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B22" s="5" t="s">
+      <c r="A22" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="3"/>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B23" s="5" t="s">
+      <c r="A23" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="3"/>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B24" s="5" t="s">
+      <c r="A24" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C24" s="3"/>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B25" s="5" t="s">
+      <c r="A25" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C25" s="3"/>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B26" s="4" t="s">
+      <c r="A26" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>27</v>
       </c>
       <c r="C26" s="3"/>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C29" s="3"/>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="4" t="s">
+      <c r="A30" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C30" s="3"/>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="4" t="s">
+      <c r="A31" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C31" s="3"/>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="4" t="s">
+      <c r="A32" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C32" s="3"/>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
+      <c r="A33" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C33" s="3"/>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C34" s="3"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C35" s="3"/>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="4" t="s">
+      <c r="A36" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C36" s="3"/>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C37" s="3"/>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="4" t="s">
+      <c r="A38" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="2" t="s">
         <v>41</v>
       </c>
       <c r="C38" s="3"/>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="2" t="s">
         <v>42</v>
       </c>
       <c r="C39" s="3"/>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C40" s="3"/>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="2" t="s">
         <v>44</v>
       </c>
       <c r="C41" s="3"/>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="4" t="s">
+      <c r="A42" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C42" s="3"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C43" s="3"/>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="2" t="s">
         <v>48</v>
       </c>
       <c r="C44" s="3"/>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="2" t="s">
         <v>49</v>
       </c>
       <c r="C45" s="3"/>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C46" s="3"/>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C47" s="3"/>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C48" s="3"/>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="2" t="s">
         <v>53</v>
       </c>
       <c r="C49" s="3"/>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C50" s="3"/>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C51" s="3"/>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C52" s="3"/>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C53" s="3"/>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="4" t="s">
+      <c r="A54" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="2" t="s">
         <v>59</v>
       </c>
       <c r="C54" s="3"/>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="2" t="s">
         <v>60</v>
       </c>
       <c r="C55" s="3"/>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="4" t="s">
+      <c r="A56" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="2" t="s">
         <v>61</v>
       </c>
       <c r="C56" s="3"/>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="4" t="s">
+      <c r="A57" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C57" s="3"/>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="4" t="s">
+      <c r="A58" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="2" t="s">
         <v>63</v>
       </c>
       <c r="C58" s="3"/>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="4" t="s">
+      <c r="A59" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C59" s="3"/>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="2" t="s">
         <v>65</v>
       </c>
       <c r="C60" s="3"/>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="4" t="s">
+      <c r="A61" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="2" t="s">
         <v>66</v>
       </c>
       <c r="C61" s="3"/>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="4" t="s">
+      <c r="A62" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C62" s="3"/>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="4" t="s">
+      <c r="A63" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C63" s="3"/>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="4" t="s">
+      <c r="A64" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="2" t="s">
         <v>70</v>
       </c>
       <c r="C64" s="3"/>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="4" t="s">
+      <c r="A65" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C65" s="3"/>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66" s="4" t="s">
+      <c r="A66" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="2" t="s">
         <v>72</v>
       </c>
       <c r="C66" s="3"/>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="4" t="s">
+      <c r="A67" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C67" s="3"/>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="4" t="s">
+      <c r="A68" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="2" t="s">
         <v>74</v>
       </c>
       <c r="C68" s="3"/>
     </row>
     <row r="69" spans="1:3">
-      <c r="A69" s="4" t="s">
+      <c r="A69" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C69" s="3"/>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70" s="4" t="s">
+      <c r="A70" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C70" s="3"/>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="4" t="s">
+      <c r="A71" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C71" s="3"/>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C72" s="3"/>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="4" t="s">
+      <c r="A73" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C73" s="3"/>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C74" s="3"/>
     </row>
     <row r="75" spans="1:3">
-      <c r="A75" s="4" t="s">
+      <c r="A75" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="2" t="s">
         <v>82</v>
       </c>
       <c r="C75" s="3"/>
     </row>
     <row r="76" spans="1:3">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="2" t="s">
         <v>83</v>
       </c>
       <c r="C76" s="3"/>
     </row>
     <row r="77" spans="1:3">
-      <c r="A77" s="4" t="s">
+      <c r="A77" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B77" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C77" s="3"/>
     </row>
     <row r="78" spans="1:3">
-      <c r="A78" s="4" t="s">
+      <c r="A78" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B78" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C78" s="3"/>
     </row>
     <row r="79" spans="1:3">
-      <c r="A79" s="4" t="s">
+      <c r="A79" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="B79" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C79" s="3"/>
     </row>
     <row r="80" spans="1:3">
-      <c r="A80" s="4" t="s">
+      <c r="A80" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B80" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C80" s="3"/>
     </row>
     <row r="81" spans="1:3">
-      <c r="A81" s="4" t="s">
+      <c r="A81" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="B81" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C81" s="3"/>
     </row>
     <row r="82" spans="1:3">
-      <c r="A82" s="4" t="s">
+      <c r="A82" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B82" s="4" t="s">
+      <c r="B82" s="2" t="s">
         <v>90</v>
       </c>
       <c r="C82" s="3"/>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="4" t="s">
+      <c r="A83" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="B83" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C83" s="3"/>
     </row>
     <row r="84" spans="1:3">
-      <c r="A84" s="4" t="s">
+      <c r="A84" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B84" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C84" s="3"/>
     </row>
     <row r="85" spans="1:3">
-      <c r="A85" s="4" t="s">
+      <c r="A85" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="2" t="s">
         <v>93</v>
       </c>
       <c r="C85" s="3"/>
     </row>
     <row r="86" spans="1:3">
-      <c r="A86" s="4" t="s">
+      <c r="A86" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="2" t="s">
         <v>94</v>
       </c>
       <c r="C86" s="3"/>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="5" t="s">
+      <c r="A87" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="B87" s="4" t="s">
         <v>95</v>
       </c>
       <c r="C87" s="3"/>
     </row>
     <row r="88" spans="1:3">
-      <c r="A88" s="5" t="s">
+      <c r="A88" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B88" s="5" t="s">
+      <c r="B88" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C88" s="3"/>
     </row>
     <row r="89" spans="1:3">
-      <c r="A89" s="5" t="s">
+      <c r="A89" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B89" s="5" t="s">
+      <c r="B89" s="4" t="s">
         <v>97</v>
       </c>
       <c r="C89" s="3"/>
     </row>
     <row r="90" spans="1:3">
-      <c r="A90" s="4" t="s">
+      <c r="A90" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="B90" s="2" t="s">
         <v>99</v>
       </c>
       <c r="C90" s="3"/>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="4" t="s">
+      <c r="A91" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C91" s="3"/>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="4" t="s">
+      <c r="A92" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B92" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C92" s="3"/>
     </row>
     <row r="93" spans="1:3">
-      <c r="A93" s="4" t="s">
+      <c r="A93" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B93" s="2" t="s">
         <v>102</v>
       </c>
       <c r="C93" s="3"/>
     </row>
     <row r="94" spans="1:3">
-      <c r="A94" s="4" t="s">
+      <c r="A94" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B94" s="2" t="s">
         <v>103</v>
       </c>
       <c r="C94" s="3"/>
     </row>
     <row r="95" spans="1:3">
-      <c r="A95" s="4" t="s">
+      <c r="A95" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B95" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C95" s="3"/>
     </row>
     <row r="96" spans="1:3">
-      <c r="A96" s="4" t="s">
+      <c r="A96" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B96" s="2" t="s">
         <v>106</v>
       </c>
       <c r="C96" s="3"/>
     </row>
     <row r="97" spans="1:3">
-      <c r="A97" s="4" t="s">
+      <c r="A97" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B97" s="5" t="s">
+      <c r="B97" s="4" t="s">
         <v>107</v>
       </c>
       <c r="C97" s="3"/>
     </row>
     <row r="98" spans="1:3">
-      <c r="A98" s="4" t="s">
+      <c r="A98" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B98" s="5" t="s">
+      <c r="B98" s="4" t="s">
         <v>109</v>
       </c>
       <c r="C98" s="3"/>
     </row>
     <row r="99" spans="1:3">
-      <c r="A99" s="4" t="s">
+      <c r="A99" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B99" s="5" t="s">
+      <c r="B99" s="4" t="s">
         <v>110</v>
       </c>
       <c r="C99" s="3"/>
     </row>
     <row r="100" spans="1:3">
-      <c r="A100" s="4" t="s">
+      <c r="A100" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B100" s="5" t="s">
+      <c r="B100" s="4" t="s">
         <v>111</v>
       </c>
       <c r="C100" s="3"/>
     </row>
     <row r="101" spans="1:3">
-      <c r="A101" s="4" t="s">
+      <c r="A101" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B101" s="5" t="s">
+      <c r="B101" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C101" s="3"/>
     </row>
     <row r="102" spans="1:3">
-      <c r="A102" s="4" t="s">
+      <c r="A102" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B102" s="5" t="s">
+      <c r="B102" s="4" t="s">
         <v>113</v>
       </c>
       <c r="C102" s="3"/>
     </row>
     <row r="103" spans="1:3">
-      <c r="A103" s="4" t="s">
+      <c r="A103" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B103" s="5" t="s">
+      <c r="B103" s="4" t="s">
         <v>114</v>
       </c>
       <c r="C103" s="3"/>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="4" t="s">
+      <c r="A104" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B104" s="5" t="s">
+      <c r="B104" s="4" t="s">
         <v>116</v>
       </c>
       <c r="C104" s="3"/>
     </row>
     <row r="105" spans="1:3">
-      <c r="A105" s="4" t="s">
+      <c r="A105" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B105" s="5" t="s">
+      <c r="B105" s="4" t="s">
         <v>117</v>
       </c>
       <c r="C105" s="3"/>
     </row>
     <row r="106" spans="1:3">
-      <c r="A106" s="4" t="s">
+      <c r="A106" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B106" s="5" t="s">
+      <c r="B106" s="4" t="s">
         <v>118</v>
       </c>
       <c r="C106" s="3"/>
     </row>
     <row r="107" spans="1:3">
-      <c r="A107" s="4" t="s">
+      <c r="A107" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B107" s="5" t="s">
+      <c r="B107" s="4" t="s">
         <v>120</v>
       </c>
       <c r="C107" s="3"/>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="4" t="s">
+      <c r="A108" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B108" s="5" t="s">
+      <c r="B108" s="4" t="s">
         <v>122</v>
       </c>
       <c r="C108" s="3"/>
     </row>
     <row r="109" spans="1:3">
-      <c r="A109" s="4" t="s">
+      <c r="A109" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B109" s="5" t="s">
+      <c r="B109" s="4" t="s">
         <v>123</v>
       </c>
       <c r="C109" s="3"/>
     </row>
     <row r="110" spans="1:3">
-      <c r="A110" s="4" t="s">
+      <c r="A110" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B110" s="4" t="s">
+      <c r="B110" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C110" s="3"/>
     </row>
     <row r="111" spans="1:3">
-      <c r="A111" s="4" t="s">
+      <c r="A111" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B111" s="4" t="s">
+      <c r="B111" s="2" t="s">
         <v>126</v>
       </c>
       <c r="C111" s="3"/>
     </row>
     <row r="112" spans="1:3">
-      <c r="A112" s="4" t="s">
+      <c r="A112" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B112" s="4" t="s">
+      <c r="B112" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C112" s="3"/>
     </row>
     <row r="113" spans="1:3">
-      <c r="A113" s="4" t="s">
+      <c r="A113" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B113" s="4" t="s">
+      <c r="B113" s="2" t="s">
         <v>129</v>
       </c>
       <c r="C113" s="3"/>
     </row>
     <row r="114" spans="1:3">
-      <c r="A114" s="4" t="s">
+      <c r="A114" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B114" s="4" t="s">
+      <c r="B114" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C114" s="3"/>
     </row>
     <row r="115" spans="1:3">
-      <c r="A115" s="4" t="s">
+      <c r="A115" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B115" s="4" t="s">
+      <c r="B115" s="2" t="s">
         <v>113</v>
       </c>
       <c r="C115" s="3"/>
     </row>
     <row r="116" spans="1:3">
-      <c r="A116" s="4" t="s">
+      <c r="A116" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B116" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C116" s="3"/>
     </row>
     <row r="117" spans="1:3">
-      <c r="A117" s="4" t="s">
+      <c r="A117" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="B117" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C117" s="3"/>
     </row>
     <row r="118" spans="1:3">
-      <c r="A118" s="4" t="s">
+      <c r="A118" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B118" s="4" t="s">
+      <c r="B118" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C118" s="3"/>
     </row>
     <row r="119" spans="1:3">
-      <c r="A119" s="4" t="s">
+      <c r="A119" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B119" s="4" t="s">
+      <c r="B119" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C119" s="3"/>
     </row>
     <row r="120" spans="1:3">
-      <c r="A120" s="4" t="s">
+      <c r="A120" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B120" s="4" t="s">
+      <c r="B120" s="2" t="s">
         <v>134</v>
       </c>
       <c r="C120" s="3"/>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="4" t="s">
+      <c r="A121" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B121" s="4" t="s">
+      <c r="B121" s="2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="122" spans="1:3">
-      <c r="A122" s="4" t="s">
+      <c r="A122" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B122" s="4" t="s">
+      <c r="B122" s="2" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="123" spans="1:3">
-      <c r="A123" s="4" t="s">
+      <c r="A123" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B123" s="4" t="s">
+      <c r="B123" s="2" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="124" spans="1:3">
-      <c r="A124" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B124" s="4" t="s">
+      <c r="A124" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="125" spans="1:3">
-      <c r="A125" s="4" t="s">
+      <c r="A125" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B125" s="4" t="s">
+      <c r="B125" s="2" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="126" spans="1:3">
-      <c r="A126" s="4" t="s">
+      <c r="A126" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B126" s="4" t="s">
+      <c r="B126" s="2" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="127" spans="1:3">
-      <c r="A127" s="4" t="s">
+      <c r="A127" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B127" s="4" t="s">
+      <c r="B127" s="2" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="4" t="s">
+      <c r="A128" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B128" s="4" t="s">
+      <c r="B128" s="2" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="4" t="s">
+      <c r="A129" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B129" s="4" t="s">
+      <c r="B129" s="2" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="130" spans="1:2">
-      <c r="A130" s="4" t="s">
+      <c r="A130" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B130" s="4" t="s">
+      <c r="B130" s="2" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="4" t="s">
+      <c r="A131" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B131" s="4" t="s">
+      <c r="B131" s="2" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="132" spans="1:2">
-      <c r="A132" s="4" t="s">
+      <c r="A132" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B132" s="4" t="s">
+      <c r="B132" s="2" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="4" t="s">
+      <c r="A133" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B133" s="4" t="s">
+      <c r="B133" s="2" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="4" t="s">
+      <c r="A134" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B134" s="4" t="s">
+      <c r="B134" s="2" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="4" t="s">
+      <c r="A135" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B135" s="4" t="s">
+      <c r="B135" s="2" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="4" t="s">
+      <c r="A136" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B136" s="4" t="s">
+      <c r="B136" s="2" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="4" t="s">
+      <c r="A137" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B137" s="4" t="s">
+      <c r="B137" s="2" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="4" t="s">
+      <c r="A138" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B138" s="4" t="s">
+      <c r="B138" s="2" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="4" t="s">
+      <c r="A139" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B139" s="4" t="s">
+      <c r="B139" s="2" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B140" s="4" t="s">
+      <c r="A140" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B140" s="2" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="4" t="s">
+      <c r="A141" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B141" s="4" t="s">
+      <c r="B141" s="2" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="142" spans="1:2">
-      <c r="A142" s="4" t="s">
+      <c r="A142" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B142" s="4" t="s">
+      <c r="B142" s="2" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="4" t="s">
+      <c r="A143" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B143" s="4" t="s">
+      <c r="B143" s="2" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="144" spans="1:2">
-      <c r="A144" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B144" s="4" t="s">
+      <c r="A144" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B144" s="2" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="4" t="s">
+      <c r="A145" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B145" s="4" t="s">
+      <c r="B145" s="2" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="4" t="s">
+      <c r="A146" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B146" s="4" t="s">
+      <c r="B146" s="2" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="4" t="s">
+      <c r="A147" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B147" s="4" t="s">
+      <c r="B147" s="2" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="4" t="s">
+      <c r="A148" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B148" s="4" t="s">
+      <c r="B148" s="2" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="4" t="s">
+      <c r="A149" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B149" s="4" t="s">
+      <c r="B149" s="2" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="4" t="s">
+      <c r="A150" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B150" s="4" t="s">
+      <c r="B150" s="2" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="4" t="s">
+      <c r="A151" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B151" s="4" t="s">
+      <c r="B151" s="2" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="4" t="s">
+      <c r="A152" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B152" s="4" t="s">
+      <c r="B152" s="2" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="4" t="s">
+      <c r="A153" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B153" s="4" t="s">
+      <c r="B153" s="2" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="154" spans="1:2">
-      <c r="A154" s="4" t="s">
+      <c r="A154" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B154" s="4" t="s">
+      <c r="B154" s="2" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="4" t="s">
+      <c r="A155" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B155" s="4" t="s">
+      <c r="B155" s="2" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="4" t="s">
+      <c r="A156" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B156" s="4" t="s">
+      <c r="B156" s="2" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="4" t="s">
+      <c r="A157" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B157" s="4" t="s">
+      <c r="B157" s="2" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="4" t="s">
+      <c r="A158" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B158" s="4" t="s">
+      <c r="B158" s="2" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="4" t="s">
+      <c r="A159" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B159" s="4" t="s">
+      <c r="B159" s="2" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="4" t="s">
+      <c r="A160" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B160" s="4" t="s">
+      <c r="B160" s="2" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="4" t="s">
+      <c r="A161" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B161" s="4" t="s">
+      <c r="B161" s="2" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="4" t="s">
+      <c r="A162" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B162" s="4" t="s">
+      <c r="B162" s="2" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="4" t="s">
+      <c r="A163" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B163" s="4" t="s">
+      <c r="B163" s="2" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="4" t="s">
+      <c r="A164" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B164" s="4" t="s">
+      <c r="B164" s="2" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="4" t="s">
+      <c r="A165" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B165" s="4" t="s">
+      <c r="B165" s="2" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="4" t="s">
+      <c r="A166" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B166" s="4" t="s">
+      <c r="B166" s="2" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="4" t="s">
+      <c r="A167" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B167" s="4" t="s">
+      <c r="B167" s="2" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="168" spans="1:2">
-      <c r="A168" s="4" t="s">
+      <c r="A168" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B168" s="4" t="s">
+      <c r="B168" s="2" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="4" t="s">
+      <c r="A169" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B169" s="4" t="s">
+      <c r="B169" s="2" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="170" spans="1:2">
-      <c r="A170" s="4" t="s">
+      <c r="A170" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B170" s="4" t="s">
+      <c r="B170" s="2" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B171" s="4" t="s">
+      <c r="A171" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B171" s="2" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="172" spans="1:2">
-      <c r="A172" s="4" t="s">
+      <c r="A172" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B172" s="4" t="s">
+      <c r="B172" s="2" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="4" t="s">
+      <c r="A173" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B173" s="4" t="s">
+      <c r="B173" s="2" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="174" spans="1:2">
-      <c r="A174" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B174" s="4" t="s">
+      <c r="A174" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B174" s="2" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="4" t="s">
+      <c r="A175" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B175" s="4" t="s">
+      <c r="B175" s="2" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="176" spans="1:2">
-      <c r="A176" s="4" t="s">
+      <c r="A176" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B176" s="4" t="s">
+      <c r="B176" s="2" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="4" t="s">
+      <c r="A177" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B177" s="4" t="s">
+      <c r="B177" s="2" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="178" spans="1:2">
-      <c r="A178" s="4" t="s">
+      <c r="A178" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B178" s="4" t="s">
+      <c r="B178" s="2" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="4" t="s">
+      <c r="A179" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B179" s="4" t="s">
+      <c r="B179" s="2" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="180" spans="1:2">
-      <c r="A180" s="4" t="s">
+      <c r="A180" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B180" s="4" t="s">
+      <c r="B180" s="2" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B181" s="4" t="s">
+      <c r="A181" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B181" s="2" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="182" spans="1:2">
-      <c r="A182" s="4" t="s">
+      <c r="A182" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B182" s="4" t="s">
+      <c r="B182" s="2" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="4" t="s">
+      <c r="A183" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B183" s="4" t="s">
+      <c r="B183" s="2" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="184" spans="1:2">
-      <c r="A184" s="4" t="s">
+      <c r="A184" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B184" s="4" t="s">
+      <c r="B184" s="2" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="4" t="s">
+      <c r="A185" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B185" s="4" t="s">
+      <c r="B185" s="2" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="186" spans="1:2">
-      <c r="A186" s="4" t="s">
+      <c r="A186" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B186" s="4" t="s">
+      <c r="B186" s="2" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="4" t="s">
+      <c r="A187" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B187" s="4" t="s">
+      <c r="B187" s="2" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="188" spans="1:2">
-      <c r="A188" s="4" t="s">
+      <c r="A188" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B188" s="4" t="s">
+      <c r="B188" s="2" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B189" s="4" t="s">
+      <c r="A189" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B189" s="2" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="190" spans="1:2">
-      <c r="A190" s="4" t="s">
+      <c r="A190" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B190" s="4" t="s">
+      <c r="B190" s="2" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="4" t="s">
+      <c r="A191" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B191" s="4" t="s">
+      <c r="B191" s="2" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="4" t="s">
+      <c r="A192" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B192" s="4" t="s">
+      <c r="B192" s="2" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="193" spans="1:2">
-      <c r="A193" s="4" t="s">
+      <c r="A193" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B193" s="4" t="s">
+      <c r="B193" s="2" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="194" spans="1:2">
-      <c r="A194" s="4" t="s">
+      <c r="A194" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B194" s="4" t="s">
+      <c r="B194" s="2" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="195" spans="1:2">
-      <c r="A195" s="4" t="s">
+      <c r="A195" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B195" s="4" t="s">
+      <c r="B195" s="2" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="196" spans="1:2">
-      <c r="A196" s="4" t="s">
+      <c r="A196" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B196" s="4" t="s">
+      <c r="B196" s="2" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="197" spans="1:2">
-      <c r="A197" s="4" t="s">
+      <c r="A197" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B197" s="4" t="s">
+      <c r="B197" s="2" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="198" spans="1:2">
-      <c r="A198" s="4" t="s">
+      <c r="A198" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B198" s="4" t="s">
+      <c r="B198" s="2" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="199" spans="1:2">
-      <c r="A199" s="4" t="s">
+      <c r="A199" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B199" s="4" t="s">
+      <c r="B199" s="2" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="200" spans="1:2">
-      <c r="A200" s="4" t="s">
+      <c r="A200" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B200" s="4" t="s">
+      <c r="B200" s="2" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="201" spans="1:2">
-      <c r="A201" s="4" t="s">
+      <c r="A201" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B201" s="4" t="s">
+      <c r="B201" s="2" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="202" spans="1:2">
-      <c r="A202" s="4" t="s">
+      <c r="A202" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B202" s="4" t="s">
+      <c r="B202" s="2" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="203" spans="1:2">
-      <c r="A203" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B203" s="4" t="s">
+      <c r="A203" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B203" s="2" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="204" spans="1:2">
-      <c r="A204" s="4" t="s">
+      <c r="A204" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B204" s="4" t="s">
+      <c r="B204" s="2" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="205" spans="1:2">
-      <c r="A205" s="4" t="s">
+      <c r="A205" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B205" s="4" t="s">
+      <c r="B205" s="2" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="206" spans="1:2">
-      <c r="A206" s="4" t="s">
+      <c r="A206" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B206" s="4" t="s">
+      <c r="B206" s="2" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="207" spans="1:2">
-      <c r="A207" s="4" t="s">
+      <c r="A207" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B207" s="4" t="s">
+      <c r="B207" s="2" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="208" spans="1:2">
-      <c r="A208" s="4" t="s">
+      <c r="A208" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B208" s="4" t="s">
+      <c r="B208" s="2" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="209" spans="1:2">
-      <c r="A209" s="4" t="s">
+      <c r="A209" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B209" s="4" t="s">
+      <c r="B209" s="2" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="210" spans="1:2">
-      <c r="A210" s="4" t="s">
+      <c r="A210" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B210" s="4" t="s">
+      <c r="B210" s="2" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="211" spans="1:2">
-      <c r="A211" s="4" t="s">
+      <c r="A211" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B211" s="4" t="s">
+      <c r="B211" s="2" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="212" spans="1:2">
-      <c r="A212" s="4" t="s">
+      <c r="A212" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B212" s="4" t="s">
+      <c r="B212" s="2" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="213" spans="1:2">
-      <c r="A213" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B213" s="4" t="s">
+      <c r="A213" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B213" s="2" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="214" spans="1:2">
-      <c r="A214" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B214" s="4" t="s">
+      <c r="A214" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B214" s="2" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="215" spans="1:2">
-      <c r="A215" s="4" t="s">
+      <c r="A215" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B215" s="4" t="s">
+      <c r="B215" s="2" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="216" spans="1:2">
-      <c r="A216" s="4" t="s">
+      <c r="A216" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B216" s="4" t="s">
+      <c r="B216" s="2" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="217" spans="1:2">
-      <c r="A217" s="4" t="s">
+      <c r="A217" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B217" s="4" t="s">
+      <c r="B217" s="2" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="218" spans="1:2">
-      <c r="A218" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B218" s="4" t="s">
+      <c r="A218" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B218" s="2" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="219" spans="1:2">
-      <c r="A219" s="4" t="s">
+      <c r="A219" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B219" s="4" t="s">
+      <c r="B219" s="2" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="220" spans="1:2">
-      <c r="A220" s="4" t="s">
+      <c r="A220" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B220" s="4" t="s">
+      <c r="B220" s="2" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B221" s="2" t="s">
-        <v>234</v>
+      <c r="A221" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="242">
   <si>
     <t>UA名字</t>
   </si>
@@ -755,6 +755,9 @@
   </si>
   <si>
     <t>7006</t>
+  </si>
+  <si>
+    <t>2090</t>
   </si>
 </sst>
 </file>
@@ -1731,7 +1734,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C226"/>
+  <dimension ref="A1:C227"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3618,51 +3621,59 @@
       </c>
     </row>
     <row r="221" spans="1:2">
-      <c r="A221" s="5" t="s">
+      <c r="A221" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B221" s="5" t="s">
+      <c r="B221" s="2" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="222" spans="1:2">
-      <c r="A222" s="5" t="s">
+      <c r="A222" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B222" s="5" t="s">
+      <c r="B222" s="2" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="223" spans="1:2">
-      <c r="A223" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B223" s="5" t="s">
+      <c r="A223" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B223" s="2" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="224" spans="1:2">
-      <c r="A224" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B224" s="5" t="s">
+      <c r="A224" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B224" s="2" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="225" spans="1:2">
-      <c r="A225" s="5" t="s">
+      <c r="A225" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B225" s="5" t="s">
+      <c r="B225" s="2" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="226" spans="1:2">
-      <c r="A226" s="5" t="s">
+      <c r="A226" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B226" s="5" t="s">
+      <c r="B226" s="2" t="s">
         <v>240</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>241</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="245">
   <si>
     <t>UA名字</t>
   </si>
@@ -758,6 +758,15 @@
   </si>
   <si>
     <t>2090</t>
+  </si>
+  <si>
+    <t>9799</t>
+  </si>
+  <si>
+    <t>8489</t>
+  </si>
+  <si>
+    <t>0006</t>
   </si>
 </sst>
 </file>
@@ -1734,7 +1743,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C227"/>
+  <dimension ref="A1:C230"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3669,11 +3678,35 @@
       </c>
     </row>
     <row r="227" spans="1:2">
-      <c r="A227" s="5" t="s">
+      <c r="A227" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B227" s="5" t="s">
+      <c r="B227" s="2" t="s">
         <v>241</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>244</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="247">
   <si>
     <t>UA名字</t>
   </si>
@@ -767,6 +767,12 @@
   </si>
   <si>
     <t>0006</t>
+  </si>
+  <si>
+    <t>6619</t>
+  </si>
+  <si>
+    <t>5162</t>
   </si>
 </sst>
 </file>
@@ -1743,7 +1749,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C230"/>
+  <dimension ref="A1:C233"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3686,27 +3692,51 @@
       </c>
     </row>
     <row r="228" spans="1:2">
-      <c r="A228" s="5" t="s">
+      <c r="A228" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B228" s="5" t="s">
+      <c r="B228" s="2" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="229" spans="1:2">
-      <c r="A229" s="5" t="s">
+      <c r="A229" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B229" s="5" t="s">
+      <c r="B229" s="2" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="230" spans="1:2">
-      <c r="A230" s="5" t="s">
+      <c r="A230" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B230" s="5" t="s">
+      <c r="B230" s="2" t="s">
         <v>244</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>246</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="249">
   <si>
     <t>UA名字</t>
   </si>
@@ -773,6 +773,12 @@
   </si>
   <si>
     <t>5162</t>
+  </si>
+  <si>
+    <t>3122</t>
+  </si>
+  <si>
+    <t>5097</t>
   </si>
 </sst>
 </file>
@@ -1749,7 +1755,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C233"/>
+  <dimension ref="A1:C235"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3716,27 +3722,43 @@
       </c>
     </row>
     <row r="231" spans="1:2">
-      <c r="A231" s="5" t="s">
+      <c r="A231" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B231" s="5" t="s">
+      <c r="B231" s="2" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="232" spans="1:2">
-      <c r="A232" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B232" s="5" t="s">
+      <c r="A232" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B232" s="2" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="233" spans="1:2">
-      <c r="A233" s="5" t="s">
+      <c r="A233" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B233" s="5" t="s">
+      <c r="B233" s="2" t="s">
         <v>246</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="250">
   <si>
     <t>UA名字</t>
   </si>
@@ -779,6 +779,9 @@
   </si>
   <si>
     <t>5097</t>
+  </si>
+  <si>
+    <t>3176</t>
   </si>
 </sst>
 </file>
@@ -1755,7 +1758,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C235"/>
+  <dimension ref="A1:C236"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3746,19 +3749,27 @@
       </c>
     </row>
     <row r="234" spans="1:2">
-      <c r="A234" s="5" t="s">
+      <c r="A234" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B234" s="5" t="s">
+      <c r="B234" s="2" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="235" spans="1:2">
-      <c r="A235" s="5" t="s">
+      <c r="A235" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B235" s="5" t="s">
+      <c r="B235" s="2" t="s">
         <v>248</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="252">
   <si>
     <t>UA名字</t>
   </si>
@@ -782,6 +782,12 @@
   </si>
   <si>
     <t>3176</t>
+  </si>
+  <si>
+    <t>2401</t>
+  </si>
+  <si>
+    <t>9401</t>
   </si>
 </sst>
 </file>
@@ -794,7 +800,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -812,6 +818,13 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF606266"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -961,12 +974,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1294,55 +1313,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1357,74 +1373,77 @@
     <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1437,6 +1456,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1758,7 +1780,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C236"/>
+  <dimension ref="A1:C238"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3765,11 +3787,27 @@
       </c>
     </row>
     <row r="236" spans="1:2">
-      <c r="A236" s="5" t="s">
+      <c r="A236" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B236" s="5" t="s">
+      <c r="B236" s="2" t="s">
         <v>249</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B237" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -800,7 +800,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -818,13 +818,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF606266"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -974,18 +967,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1313,52 +1300,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1373,77 +1363,74 @@
     <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1456,9 +1443,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3798,7 +3782,7 @@
       <c r="A237" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B237" s="6" t="s">
+      <c r="B237" s="2" t="s">
         <v>250</v>
       </c>
     </row>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="253">
   <si>
     <t>UA名字</t>
   </si>
@@ -788,6 +788,9 @@
   </si>
   <si>
     <t>9401</t>
+  </si>
+  <si>
+    <t>9252</t>
   </si>
 </sst>
 </file>
@@ -1764,7 +1767,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C238"/>
+  <dimension ref="A1:C239"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3779,7 +3782,7 @@
       </c>
     </row>
     <row r="237" spans="1:2">
-      <c r="A237" s="5" t="s">
+      <c r="A237" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B237" s="2" t="s">
@@ -3787,11 +3790,19 @@
       </c>
     </row>
     <row r="238" spans="1:2">
-      <c r="A238" s="5" t="s">
+      <c r="A238" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B238" s="5" t="s">
+      <c r="B238" s="2" t="s">
         <v>251</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="254">
   <si>
     <t>UA名字</t>
   </si>
@@ -791,6 +791,9 @@
   </si>
   <si>
     <t>9252</t>
+  </si>
+  <si>
+    <t>0022</t>
   </si>
 </sst>
 </file>
@@ -1433,7 +1436,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1443,9 +1446,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1767,7 +1767,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C239"/>
+  <dimension ref="A1:C240"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3798,11 +3798,19 @@
       </c>
     </row>
     <row r="239" spans="1:2">
-      <c r="A239" s="5" t="s">
+      <c r="A239" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B239" s="5" t="s">
+      <c r="B239" s="2" t="s">
         <v>252</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" t="s">
+        <v>85</v>
+      </c>
+      <c r="B240" t="s">
+        <v>253</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="270">
   <si>
     <t>UA名字</t>
   </si>
@@ -794,6 +794,54 @@
   </si>
   <si>
     <t>0022</t>
+  </si>
+  <si>
+    <t>7262</t>
+  </si>
+  <si>
+    <t>alex</t>
+  </si>
+  <si>
+    <t>3923</t>
+  </si>
+  <si>
+    <t>8282</t>
+  </si>
+  <si>
+    <t>4349</t>
+  </si>
+  <si>
+    <t>5800</t>
+  </si>
+  <si>
+    <t>7179</t>
+  </si>
+  <si>
+    <t>2695</t>
+  </si>
+  <si>
+    <t>6336</t>
+  </si>
+  <si>
+    <t>1237</t>
+  </si>
+  <si>
+    <t>9227</t>
+  </si>
+  <si>
+    <t>4571</t>
+  </si>
+  <si>
+    <t>0573</t>
+  </si>
+  <si>
+    <t>1057</t>
+  </si>
+  <si>
+    <t>7682</t>
+  </si>
+  <si>
+    <t>3406</t>
   </si>
 </sst>
 </file>
@@ -1767,7 +1815,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C240"/>
+  <dimension ref="A1:C256"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3813,6 +3861,134 @@
         <v>253</v>
       </c>
     </row>
+    <row r="241" spans="1:2">
+      <c r="A241" t="s">
+        <v>56</v>
+      </c>
+      <c r="B241" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" t="s">
+        <v>255</v>
+      </c>
+      <c r="B242" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" t="s">
+        <v>85</v>
+      </c>
+      <c r="B243" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" t="s">
+        <v>47</v>
+      </c>
+      <c r="B244" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" t="s">
+        <v>255</v>
+      </c>
+      <c r="B245" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" t="s">
+        <v>2</v>
+      </c>
+      <c r="B246" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" t="s">
+        <v>2</v>
+      </c>
+      <c r="B247" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" t="s">
+        <v>125</v>
+      </c>
+      <c r="B248" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" t="s">
+        <v>39</v>
+      </c>
+      <c r="B249" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" t="s">
+        <v>28</v>
+      </c>
+      <c r="B250" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" t="s">
+        <v>255</v>
+      </c>
+      <c r="B251" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" t="s">
+        <v>104</v>
+      </c>
+      <c r="B252" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" t="s">
+        <v>68</v>
+      </c>
+      <c r="B253" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" t="s">
+        <v>115</v>
+      </c>
+      <c r="B254" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" t="s">
+        <v>108</v>
+      </c>
+      <c r="B255" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" t="s">
+        <v>128</v>
+      </c>
+      <c r="B256" t="s">
+        <v>269</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="271">
   <si>
     <t>UA名字</t>
   </si>
@@ -842,6 +842,9 @@
   </si>
   <si>
     <t>3406</t>
+  </si>
+  <si>
+    <t>4658</t>
   </si>
 </sst>
 </file>
@@ -1484,7 +1487,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1494,6 +1497,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1815,7 +1821,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C256"/>
+  <dimension ref="A1:C257"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3989,6 +3995,14 @@
         <v>269</v>
       </c>
     </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -808,7 +808,7 @@
     <t>8282</t>
   </si>
   <si>
-    <t>4349</t>
+    <t>4249</t>
   </si>
   <si>
     <t>5800</t>
@@ -3900,10 +3900,10 @@
       </c>
     </row>
     <row r="245" spans="1:2">
-      <c r="A245" t="s">
+      <c r="A245" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="B245" t="s">
+      <c r="B245" s="5" t="s">
         <v>258</v>
       </c>
     </row>
@@ -3996,10 +3996,10 @@
       </c>
     </row>
     <row r="257" spans="1:2">
-      <c r="A257" s="5" t="s">
+      <c r="A257" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B257" s="5" t="s">
+      <c r="B257" s="2" t="s">
         <v>270</v>
       </c>
     </row>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="275">
   <si>
     <t>UA名字</t>
   </si>
@@ -845,6 +845,18 @@
   </si>
   <si>
     <t>4658</t>
+  </si>
+  <si>
+    <t>4459</t>
+  </si>
+  <si>
+    <t>0444</t>
+  </si>
+  <si>
+    <t>6652</t>
+  </si>
+  <si>
+    <t>8926</t>
   </si>
 </sst>
 </file>
@@ -1821,7 +1833,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C257"/>
+  <dimension ref="A1:C261"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -3900,10 +3912,10 @@
       </c>
     </row>
     <row r="245" spans="1:2">
-      <c r="A245" s="5" t="s">
+      <c r="A245" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B245" s="5" t="s">
+      <c r="B245" s="2" t="s">
         <v>258</v>
       </c>
     </row>
@@ -4001,6 +4013,38 @@
       </c>
       <c r="B257" s="2" t="s">
         <v>270</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B261" s="5" t="s">
+        <v>274</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="281">
   <si>
     <t>UA名字</t>
   </si>
@@ -857,6 +857,24 @@
   </si>
   <si>
     <t>8926</t>
+  </si>
+  <si>
+    <t>3808</t>
+  </si>
+  <si>
+    <t>6986</t>
+  </si>
+  <si>
+    <t>9080</t>
+  </si>
+  <si>
+    <t>5690</t>
+  </si>
+  <si>
+    <t>8278</t>
+  </si>
+  <si>
+    <t>7845</t>
   </si>
 </sst>
 </file>
@@ -1833,7 +1851,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C261"/>
+  <dimension ref="A1:C267"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -4040,11 +4058,59 @@
       </c>
     </row>
     <row r="261" spans="1:2">
-      <c r="A261" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B261" s="5" t="s">
+      <c r="A261" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B261" s="2" t="s">
         <v>274</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B262" s="5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>280</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="282">
   <si>
     <t>UA名字</t>
   </si>
@@ -875,6 +875,9 @@
   </si>
   <si>
     <t>7845</t>
+  </si>
+  <si>
+    <t>0850</t>
   </si>
 </sst>
 </file>
@@ -1851,7 +1854,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C267"/>
+  <dimension ref="A1:C268"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -4066,51 +4069,59 @@
       </c>
     </row>
     <row r="262" spans="1:2">
-      <c r="A262" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B262" s="5" t="s">
+      <c r="A262" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B262" s="2" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="263" spans="1:2">
-      <c r="A263" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B263" s="5" t="s">
+      <c r="A263" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B263" s="2" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="264" spans="1:2">
-      <c r="A264" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B264" s="5" t="s">
+      <c r="A264" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B264" s="2" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="265" spans="1:2">
-      <c r="A265" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B265" s="5" t="s">
+      <c r="A265" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B265" s="2" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="266" spans="1:2">
-      <c r="A266" s="5" t="s">
+      <c r="A266" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B266" s="5" t="s">
+      <c r="B266" s="2" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="267" spans="1:2">
-      <c r="A267" s="5" t="s">
+      <c r="A267" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B267" s="5" t="s">
+      <c r="B267" s="2" t="s">
         <v>280</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>281</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="283">
   <si>
     <t>UA名字</t>
   </si>
@@ -878,6 +878,9 @@
   </si>
   <si>
     <t>0850</t>
+  </si>
+  <si>
+    <t>1584</t>
   </si>
 </sst>
 </file>
@@ -1854,7 +1857,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C268"/>
+  <dimension ref="A1:C269"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -4117,11 +4120,19 @@
       </c>
     </row>
     <row r="268" spans="1:2">
-      <c r="A268" s="5" t="s">
+      <c r="A268" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B268" s="5" t="s">
+      <c r="B268" s="2" t="s">
         <v>281</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B269" s="5" t="s">
+        <v>282</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="285">
   <si>
     <t>UA名字</t>
   </si>
@@ -881,6 +881,12 @@
   </si>
   <si>
     <t>1584</t>
+  </si>
+  <si>
+    <t>1990</t>
+  </si>
+  <si>
+    <t>2001</t>
   </si>
 </sst>
 </file>
@@ -1857,7 +1863,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C269"/>
+  <dimension ref="A1:C271"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -4128,11 +4134,27 @@
       </c>
     </row>
     <row r="269" spans="1:2">
-      <c r="A269" s="5" t="s">
+      <c r="A269" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B269" s="5" t="s">
+      <c r="B269" s="2" t="s">
         <v>282</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B270" s="5" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B271" s="5" t="s">
+        <v>284</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="288">
   <si>
     <t>UA名字</t>
   </si>
@@ -887,6 +887,15 @@
   </si>
   <si>
     <t>2001</t>
+  </si>
+  <si>
+    <t>2493</t>
+  </si>
+  <si>
+    <t>8094</t>
+  </si>
+  <si>
+    <t>9372</t>
   </si>
 </sst>
 </file>
@@ -1863,7 +1872,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C271"/>
+  <dimension ref="A1:C274"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -4142,19 +4151,43 @@
       </c>
     </row>
     <row r="270" spans="1:2">
-      <c r="A270" s="5" t="s">
+      <c r="A270" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B270" s="5" t="s">
+      <c r="B270" s="2" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="271" spans="1:2">
-      <c r="A271" s="5" t="s">
+      <c r="A271" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B271" s="5" t="s">
+      <c r="B271" s="2" t="s">
         <v>284</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B272" s="5" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B273" s="5" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B274" s="5" t="s">
+        <v>287</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="289">
   <si>
     <t>UA名字</t>
   </si>
@@ -896,6 +896,9 @@
   </si>
   <si>
     <t>9372</t>
+  </si>
+  <si>
+    <t>1</t>
   </si>
 </sst>
 </file>
@@ -1538,7 +1541,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1548,9 +1551,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1872,7 +1872,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C274"/>
+  <dimension ref="A1:C275"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="2" width="8.88888888888889" style="1"/>
@@ -4167,27 +4167,33 @@
       </c>
     </row>
     <row r="272" spans="1:2">
-      <c r="A272" s="5" t="s">
+      <c r="A272" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B272" s="5" t="s">
+      <c r="B272" s="2" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="273" spans="1:2">
-      <c r="A273" s="5" t="s">
+      <c r="A273" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B273" s="5" t="s">
+      <c r="B273" s="2" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="274" spans="1:2">
-      <c r="A274" s="5" t="s">
+      <c r="A274" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B274" s="5" t="s">
+      <c r="B274" s="2" t="s">
         <v>287</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" s="2"/>
+      <c r="B275" s="1" t="s">
+        <v>288</v>
       </c>
     </row>
   </sheetData>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="288">
   <si>
     <t>UA名字</t>
   </si>
@@ -896,9 +896,6 @@
   </si>
   <si>
     <t>9372</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
 </sst>
 </file>
@@ -4192,9 +4189,6 @@
     </row>
     <row r="275" spans="1:2">
       <c r="A275" s="2"/>
-      <c r="B275" s="1" t="s">
-        <v>288</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tim字典.xlsx
+++ b/Tim字典.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="289">
   <si>
     <t>UA名字</t>
   </si>
@@ -896,6 +896,9 @@
   </si>
   <si>
     <t>9372</t>
+  </si>
+  <si>
+    <t>4698</t>
   </si>
 </sst>
 </file>
@@ -1538,7 +1541,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1548,6 +1551,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4188,7 +4194,12 @@
       </c>
     </row>
     <row r="275" spans="1:2">
-      <c r="A275" s="2"/>
+      <c r="A275" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>288</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
